--- a/resources/Marks/2026/even/Computational Astrophysics.xlsx
+++ b/resources/Marks/2026/even/Computational Astrophysics.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gusindia01-my.sharepoint.com/personal/nitesh_kumar_ddn_upes_ac_in/Documents/UPES/2026/Jan-May-2026/Computational Astrophysics/Marks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2063" documentId="11_3FC952BF37FB7C428065D6D94F732ED04C5A5A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27B6FA7B-2E65-422C-8848-847569281BAE}"/>
+  <xr:revisionPtr revIDLastSave="2502" documentId="11_3FC952BF37FB7C428065D6D94F732ED04C5A5A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C4734DE-42D6-4D4D-B04B-1243B79213FF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="553" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Marksheet" sheetId="2" r:id="rId1"/>
     <sheet name="Quiz 1" sheetId="10" r:id="rId2"/>
-    <sheet name="Class Test 1" sheetId="7" r:id="rId3"/>
-    <sheet name="Assignment 1" sheetId="6" r:id="rId4"/>
-    <sheet name="Mid Sem" sheetId="5" r:id="rId5"/>
-    <sheet name="Quiz 2" sheetId="11" r:id="rId6"/>
-    <sheet name="Assignment 2" sheetId="9" r:id="rId7"/>
+    <sheet name="Quiz 2" sheetId="13" r:id="rId3"/>
+    <sheet name="Class Test 1" sheetId="7" r:id="rId4"/>
+    <sheet name="Assignment 1" sheetId="6" r:id="rId5"/>
+    <sheet name="Assignment 2" sheetId="12" r:id="rId6"/>
+    <sheet name="Mid Sem" sheetId="5" r:id="rId7"/>
     <sheet name="Class Test 2" sheetId="8" r:id="rId8"/>
     <sheet name="End Sem" sheetId="4" r:id="rId9"/>
   </sheets>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="86">
   <si>
     <t>Final Marks</t>
   </si>
@@ -308,7 +308,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,8 +376,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -410,6 +416,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,7 +563,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -690,11 +702,26 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -705,13 +732,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1041,47 +1068,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="56"/>
+      <c r="A1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="63"/>
       <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:20" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="56"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="63"/>
       <c r="R2" s="33"/>
     </row>
     <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
@@ -1163,9 +1190,11 @@
         <v>15</v>
       </c>
       <c r="H4" s="16">
+        <f>'Assignment 2'!AG5*1.5/32</f>
         <v>15</v>
       </c>
       <c r="I4" s="16">
+        <f>'Class Test 2'!N5/2</f>
         <v>20</v>
       </c>
       <c r="J4" s="16">
@@ -1184,6 +1213,7 @@
         <v>100</v>
       </c>
       <c r="N4" s="16">
+        <f>'End Sem'!N5</f>
         <v>100</v>
       </c>
       <c r="O4" s="16">
@@ -1217,30 +1247,45 @@
         <f>'Class Test 1'!O6/2</f>
         <v>10</v>
       </c>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
+      <c r="G5" s="66">
+        <f>'Quiz 2'!K6*1.5/5</f>
+        <v>15</v>
+      </c>
+      <c r="H5" s="57">
+        <f>'Assignment 2'!AG6*1.5/32</f>
+        <v>15</v>
+      </c>
+      <c r="I5" s="60">
+        <f>'Class Test 2'!N6/2</f>
+        <v>16.5</v>
+      </c>
       <c r="J5" s="12">
         <f t="shared" ref="J5:J16" si="0">SUM(D5:I5)</f>
-        <v>36.4</v>
+        <v>82.9</v>
       </c>
       <c r="K5" s="12">
         <f t="shared" ref="K5:K16" si="1">J5/2</f>
-        <v>18.2</v>
-      </c>
-      <c r="L5" s="59">
+        <v>41.45</v>
+      </c>
+      <c r="L5" s="12">
         <f t="shared" ref="L5:L16" si="2">M5/5</f>
         <v>8.4</v>
       </c>
-      <c r="M5" s="17">
+      <c r="M5" s="12">
         <f>'Mid Sem'!N6</f>
         <v>42</v>
       </c>
-      <c r="N5" s="17"/>
-      <c r="O5" s="28"/>
+      <c r="N5" s="12">
+        <f>'End Sem'!N6</f>
+        <v>51</v>
+      </c>
+      <c r="O5" s="12">
+        <f>N5*0.3</f>
+        <v>15.299999999999999</v>
+      </c>
       <c r="P5" s="5">
         <f t="shared" ref="P5:P16" si="3">SUM(K5,L5,O5)</f>
-        <v>26.6</v>
+        <v>65.150000000000006</v>
       </c>
       <c r="Q5" s="34"/>
       <c r="S5" s="26" t="s">
@@ -1270,30 +1315,45 @@
         <f>'Class Test 1'!O7/2</f>
         <v>16.5</v>
       </c>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
+      <c r="G6" s="66">
+        <f>'Quiz 2'!K7*1.5/5</f>
+        <v>6</v>
+      </c>
+      <c r="H6" s="57">
+        <f>'Assignment 2'!AG7*1.5/32</f>
+        <v>15</v>
+      </c>
+      <c r="I6" s="60">
+        <f>'Class Test 2'!N7/2</f>
+        <v>16.25</v>
+      </c>
       <c r="J6" s="12">
         <f t="shared" si="0"/>
-        <v>30.8</v>
+        <v>68.05</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>15.4</v>
-      </c>
-      <c r="L6" s="59">
+        <v>34.024999999999999</v>
+      </c>
+      <c r="L6" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M6" s="17">
+      <c r="M6" s="12">
         <f>'Mid Sem'!N7</f>
         <v>0</v>
       </c>
-      <c r="N6" s="17"/>
-      <c r="O6" s="28"/>
+      <c r="N6" s="12">
+        <f>'End Sem'!N7</f>
+        <v>31</v>
+      </c>
+      <c r="O6" s="12">
+        <f t="shared" ref="O6:O16" si="4">N6*0.3</f>
+        <v>9.2999999999999989</v>
+      </c>
       <c r="P6" s="5">
-        <f t="shared" si="3"/>
-        <v>15.4</v>
+        <f>SUM(K6,L6,O6)</f>
+        <v>43.324999999999996</v>
       </c>
       <c r="Q6" s="34"/>
       <c r="S6" s="26" t="s">
@@ -1323,30 +1383,45 @@
         <f>'Class Test 1'!O8/2</f>
         <v>16.5</v>
       </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
+      <c r="G7" s="66">
+        <f>'Quiz 2'!K8*1.5/5</f>
+        <v>14.7</v>
+      </c>
+      <c r="H7" s="57">
+        <f>'Assignment 2'!AG8*1.5/32</f>
+        <v>14.953125</v>
+      </c>
+      <c r="I7" s="60">
+        <f>'Class Test 2'!N8/2</f>
+        <v>17.5</v>
+      </c>
       <c r="J7" s="12">
         <f t="shared" si="0"/>
-        <v>45.400000000000006</v>
+        <v>92.553125000000009</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>22.700000000000003</v>
-      </c>
-      <c r="L7" s="59">
+        <v>46.276562500000004</v>
+      </c>
+      <c r="L7" s="12">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="M7" s="17">
+      <c r="M7" s="12">
         <f>'Mid Sem'!N8</f>
         <v>40</v>
       </c>
-      <c r="N7" s="17"/>
-      <c r="O7" s="28"/>
+      <c r="N7" s="12">
+        <f>'End Sem'!N8</f>
+        <v>30</v>
+      </c>
+      <c r="O7" s="12">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
       <c r="P7" s="5">
         <f t="shared" si="3"/>
-        <v>30.700000000000003</v>
+        <v>63.276562500000004</v>
       </c>
       <c r="Q7" s="34"/>
       <c r="S7" s="26" t="s">
@@ -1376,30 +1451,45 @@
         <f>'Class Test 1'!O9/2</f>
         <v>19</v>
       </c>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
+      <c r="G8" s="66">
+        <f>'Quiz 2'!K9*1.5/5</f>
+        <v>14.4</v>
+      </c>
+      <c r="H8" s="57">
+        <f>'Assignment 2'!AG9*1.5/32</f>
+        <v>15</v>
+      </c>
+      <c r="I8" s="60">
+        <f>'Class Test 2'!N9/2</f>
+        <v>20</v>
+      </c>
       <c r="J8" s="12">
         <f t="shared" si="0"/>
-        <v>48.4</v>
+        <v>97.8</v>
       </c>
       <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>24.2</v>
-      </c>
-      <c r="L8" s="59">
+        <v>48.9</v>
+      </c>
+      <c r="L8" s="12">
         <f t="shared" si="2"/>
         <v>18.399999999999999</v>
       </c>
-      <c r="M8" s="17">
+      <c r="M8" s="12">
         <f>'Mid Sem'!N9</f>
         <v>92</v>
       </c>
-      <c r="N8" s="17"/>
-      <c r="O8" s="28"/>
+      <c r="N8" s="12">
+        <f>'End Sem'!N9</f>
+        <v>94</v>
+      </c>
+      <c r="O8" s="12">
+        <f t="shared" si="4"/>
+        <v>28.2</v>
+      </c>
       <c r="P8" s="5">
         <f t="shared" si="3"/>
-        <v>42.599999999999994</v>
+        <v>95.5</v>
       </c>
       <c r="Q8" s="34"/>
       <c r="S8" s="26" t="s">
@@ -1429,30 +1519,45 @@
         <f>'Class Test 1'!O10/2</f>
         <v>15.5</v>
       </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
+      <c r="G9" s="66">
+        <f>'Quiz 2'!K10*1.5/5</f>
+        <v>12.3</v>
+      </c>
+      <c r="H9" s="57">
+        <f>'Assignment 2'!AG10*1.5/32</f>
+        <v>15</v>
+      </c>
+      <c r="I9" s="60">
+        <f>'Class Test 2'!N10/2</f>
+        <v>15.5</v>
+      </c>
       <c r="J9" s="12">
         <f t="shared" si="0"/>
-        <v>36.1</v>
+        <v>78.900000000000006</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>18.05</v>
-      </c>
-      <c r="L9" s="59">
+        <v>39.450000000000003</v>
+      </c>
+      <c r="L9" s="12">
         <f t="shared" si="2"/>
         <v>12.2</v>
       </c>
-      <c r="M9" s="17">
+      <c r="M9" s="12">
         <f>'Mid Sem'!N10</f>
         <v>61</v>
       </c>
-      <c r="N9" s="17"/>
-      <c r="O9" s="28"/>
+      <c r="N9" s="12">
+        <f>'End Sem'!N10</f>
+        <v>70</v>
+      </c>
+      <c r="O9" s="12">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
       <c r="P9" s="5">
         <f t="shared" si="3"/>
-        <v>30.25</v>
+        <v>72.650000000000006</v>
       </c>
       <c r="Q9" s="34"/>
       <c r="S9" s="26" t="s">
@@ -1482,30 +1587,45 @@
         <f>'Class Test 1'!O11/2</f>
         <v>19.5</v>
       </c>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
+      <c r="G10" s="66">
+        <f>'Quiz 2'!K11*1.5/5</f>
+        <v>15</v>
+      </c>
+      <c r="H10" s="57">
+        <f>'Assignment 2'!AG11*1.5/32</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="60">
+        <f>'Class Test 2'!N11/2</f>
+        <v>13</v>
+      </c>
       <c r="J10" s="12">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="K10" s="12">
         <f t="shared" si="1"/>
-        <v>23.5</v>
-      </c>
-      <c r="L10" s="59">
+        <v>37.5</v>
+      </c>
+      <c r="L10" s="12">
         <f t="shared" si="2"/>
         <v>15.2</v>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="12">
         <f>'Mid Sem'!N11</f>
         <v>76</v>
       </c>
-      <c r="N10" s="17"/>
-      <c r="O10" s="28"/>
+      <c r="N10" s="12">
+        <f>'End Sem'!N11</f>
+        <v>66</v>
+      </c>
+      <c r="O10" s="12">
+        <f t="shared" si="4"/>
+        <v>19.8</v>
+      </c>
       <c r="P10" s="5">
         <f t="shared" si="3"/>
-        <v>38.700000000000003</v>
+        <v>72.5</v>
       </c>
       <c r="Q10" s="34"/>
       <c r="S10" s="26" t="s">
@@ -1535,30 +1655,45 @@
         <f>'Class Test 1'!O12/2</f>
         <v>0</v>
       </c>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
+      <c r="G11" s="66">
+        <f>'Quiz 2'!K12*1.5/5</f>
+        <v>15</v>
+      </c>
+      <c r="H11" s="57">
+        <f>'Assignment 2'!AG12*1.5/32</f>
+        <v>15</v>
+      </c>
+      <c r="I11" s="60">
+        <f>'Class Test 2'!N12/2</f>
+        <v>16</v>
+      </c>
       <c r="J11" s="12">
         <f t="shared" si="0"/>
-        <v>10.5</v>
+        <v>56.5</v>
       </c>
       <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>5.25</v>
-      </c>
-      <c r="L11" s="59">
+        <v>28.25</v>
+      </c>
+      <c r="L11" s="12">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="M11" s="17">
+      <c r="M11" s="12">
         <f>'Mid Sem'!N12</f>
         <v>35</v>
       </c>
-      <c r="N11" s="17"/>
-      <c r="O11" s="28"/>
+      <c r="N11" s="12">
+        <f>'End Sem'!N12</f>
+        <v>71</v>
+      </c>
+      <c r="O11" s="12">
+        <f t="shared" si="4"/>
+        <v>21.3</v>
+      </c>
       <c r="P11" s="5">
         <f t="shared" si="3"/>
-        <v>12.25</v>
+        <v>56.55</v>
       </c>
       <c r="Q11" s="34"/>
       <c r="S11" s="26" t="s">
@@ -1588,30 +1723,45 @@
         <f>'Class Test 1'!O13/2</f>
         <v>0</v>
       </c>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
+      <c r="G12" s="66">
+        <f>'Quiz 2'!K13*1.5/5</f>
+        <v>14.1</v>
+      </c>
+      <c r="H12" s="57">
+        <f>'Assignment 2'!AG13*1.5/32</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="60">
+        <f>'Class Test 2'!N13/2</f>
+        <v>15</v>
+      </c>
       <c r="J12" s="12">
         <f t="shared" si="0"/>
-        <v>25.2</v>
+        <v>54.3</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>12.6</v>
-      </c>
-      <c r="L12" s="59">
+        <v>27.15</v>
+      </c>
+      <c r="L12" s="12">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="M12" s="17">
+      <c r="M12" s="12">
         <f>'Mid Sem'!N13</f>
         <v>30</v>
       </c>
-      <c r="N12" s="17"/>
-      <c r="O12" s="28"/>
+      <c r="N12" s="12">
+        <f>'End Sem'!N13</f>
+        <v>41</v>
+      </c>
+      <c r="O12" s="12">
+        <f t="shared" si="4"/>
+        <v>12.299999999999999</v>
+      </c>
       <c r="P12" s="5">
         <f t="shared" si="3"/>
-        <v>18.600000000000001</v>
+        <v>45.449999999999996</v>
       </c>
       <c r="Q12" s="34"/>
       <c r="S12" s="26" t="s">
@@ -1641,30 +1791,45 @@
         <f>'Class Test 1'!O14/2</f>
         <v>9</v>
       </c>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
+      <c r="G13" s="66">
+        <f>'Quiz 2'!K14*1.5/5</f>
+        <v>15</v>
+      </c>
+      <c r="H13" s="57">
+        <f>'Assignment 2'!AG14*1.5/32</f>
+        <v>14.625</v>
+      </c>
+      <c r="I13" s="60">
+        <f>'Class Test 2'!N14/2</f>
+        <v>15.5</v>
+      </c>
       <c r="J13" s="12">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>81.625</v>
       </c>
       <c r="K13" s="12">
         <f t="shared" si="1"/>
-        <v>18.25</v>
-      </c>
-      <c r="L13" s="59">
+        <v>40.8125</v>
+      </c>
+      <c r="L13" s="12">
         <f t="shared" si="2"/>
         <v>9.4</v>
       </c>
-      <c r="M13" s="17">
+      <c r="M13" s="12">
         <f>'Mid Sem'!N14</f>
         <v>47</v>
       </c>
-      <c r="N13" s="17"/>
-      <c r="O13" s="28"/>
+      <c r="N13" s="12">
+        <f>'End Sem'!N14</f>
+        <v>64</v>
+      </c>
+      <c r="O13" s="12">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
       <c r="P13" s="5">
         <f t="shared" si="3"/>
-        <v>27.65</v>
+        <v>69.412499999999994</v>
       </c>
       <c r="Q13" s="34"/>
       <c r="S13" s="26" t="s">
@@ -1694,30 +1859,45 @@
         <f>'Class Test 1'!O15/2</f>
         <v>17.75</v>
       </c>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
+      <c r="G14" s="66">
+        <f>'Quiz 2'!K15*1.5/5</f>
+        <v>14.7</v>
+      </c>
+      <c r="H14" s="57">
+        <f>'Assignment 2'!AG15*1.5/32</f>
+        <v>14.71875</v>
+      </c>
+      <c r="I14" s="60">
+        <f>'Class Test 2'!N15/2</f>
+        <v>20</v>
+      </c>
       <c r="J14" s="12">
         <f t="shared" si="0"/>
-        <v>47.35</v>
+        <v>96.768749999999997</v>
       </c>
       <c r="K14" s="12">
         <f t="shared" si="1"/>
-        <v>23.675000000000001</v>
-      </c>
-      <c r="L14" s="59">
+        <v>48.384374999999999</v>
+      </c>
+      <c r="L14" s="12">
         <f t="shared" si="2"/>
         <v>18.399999999999999</v>
       </c>
-      <c r="M14" s="17">
+      <c r="M14" s="12">
         <f>'Mid Sem'!N15</f>
         <v>92</v>
       </c>
-      <c r="N14" s="17"/>
-      <c r="O14" s="28"/>
+      <c r="N14" s="12">
+        <f>'End Sem'!N15</f>
+        <v>66</v>
+      </c>
+      <c r="O14" s="12">
+        <f t="shared" si="4"/>
+        <v>19.8</v>
+      </c>
       <c r="P14" s="5">
         <f t="shared" si="3"/>
-        <v>42.075000000000003</v>
+        <v>86.584374999999994</v>
       </c>
       <c r="Q14" s="34"/>
       <c r="S14" s="26" t="s">
@@ -1747,30 +1927,45 @@
         <f>'Class Test 1'!O16/2</f>
         <v>20</v>
       </c>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
+      <c r="G15" s="66">
+        <f>'Quiz 2'!K16*1.5/5</f>
+        <v>15</v>
+      </c>
+      <c r="H15" s="57">
+        <f>'Assignment 2'!AG16*1.5/32</f>
+        <v>14.71875</v>
+      </c>
+      <c r="I15" s="60">
+        <f>'Class Test 2'!N16/2</f>
+        <v>19</v>
+      </c>
       <c r="J15" s="12">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>96.71875</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="L15" s="59">
+        <v>48.359375</v>
+      </c>
+      <c r="L15" s="12">
         <f t="shared" si="2"/>
         <v>17.2</v>
       </c>
-      <c r="M15" s="17">
+      <c r="M15" s="12">
         <f>'Mid Sem'!N16</f>
         <v>86</v>
       </c>
-      <c r="N15" s="17"/>
-      <c r="O15" s="28"/>
+      <c r="N15" s="12">
+        <f>'End Sem'!N16</f>
+        <v>88</v>
+      </c>
+      <c r="O15" s="12">
+        <f t="shared" si="4"/>
+        <v>26.4</v>
+      </c>
       <c r="P15" s="5">
         <f t="shared" si="3"/>
-        <v>41.2</v>
+        <v>91.959374999999994</v>
       </c>
       <c r="Q15" s="34"/>
       <c r="S15" s="26" t="s">
@@ -1800,30 +1995,45 @@
         <f>'Class Test 1'!O17/2</f>
         <v>12</v>
       </c>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
+      <c r="G16" s="66">
+        <f>'Quiz 2'!K17*1.5/5</f>
+        <v>14.1</v>
+      </c>
+      <c r="H16" s="57">
+        <f>'Assignment 2'!AG17*1.5/32</f>
+        <v>15</v>
+      </c>
+      <c r="I16" s="60">
+        <f>'Class Test 2'!N17/2</f>
+        <v>16.5</v>
+      </c>
       <c r="J16" s="12">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>85.6</v>
       </c>
       <c r="K16" s="12">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L16" s="59">
+        <v>42.8</v>
+      </c>
+      <c r="L16" s="12">
         <f t="shared" si="2"/>
         <v>6.4</v>
       </c>
-      <c r="M16" s="17">
+      <c r="M16" s="12">
         <f>'Mid Sem'!N17</f>
         <v>32</v>
       </c>
-      <c r="N16" s="17"/>
-      <c r="O16" s="28"/>
+      <c r="N16" s="12">
+        <f>'End Sem'!N17</f>
+        <v>42</v>
+      </c>
+      <c r="O16" s="12">
+        <f t="shared" si="4"/>
+        <v>12.6</v>
+      </c>
       <c r="P16" s="5">
         <f t="shared" si="3"/>
-        <v>26.4</v>
+        <v>61.8</v>
       </c>
       <c r="Q16" s="34"/>
       <c r="S16" s="26" t="s">
@@ -1852,7 +2062,7 @@
       <c r="P17" s="42"/>
       <c r="Q17" s="43"/>
       <c r="U17" t="str">
-        <f t="shared" ref="U17" si="4">LOWER(S17)</f>
+        <f t="shared" ref="U17" si="5">LOWER(S17)</f>
         <v/>
       </c>
     </row>
@@ -1891,7 +2101,7 @@
       <c r="O19" s="28"/>
       <c r="P19" s="7"/>
     </row>
-    <row r="20" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="29"/>
       <c r="B20" s="30"/>
       <c r="C20" t="s">
@@ -1902,23 +2112,53 @@
         <v>14.9</v>
       </c>
       <c r="E20">
-        <f t="shared" ref="E20:F20" si="5">MAX(E5:E16)</f>
+        <f t="shared" ref="E20:Q20" si="6">MAX(E5:E16)</f>
         <v>14.700000000000001</v>
       </c>
       <c r="F20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="7"/>
+      <c r="G20">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="6"/>
+        <v>97.8</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="6"/>
+        <v>48.9</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="6"/>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="6"/>
+        <v>92</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="6"/>
+        <v>94</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="6"/>
+        <v>28.2</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="6"/>
+        <v>95.5</v>
+      </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
@@ -1929,12 +2169,52 @@
         <v>13.7</v>
       </c>
       <c r="E21">
-        <f t="shared" ref="E21:F21" si="6">_xlfn.MINIFS(E5:E16,E5:E16, "&gt;0")</f>
+        <f t="shared" ref="E21:Q21" si="7">_xlfn.MINIFS(E5:E16,E5:E16, "&gt;0")</f>
         <v>6</v>
       </c>
       <c r="F21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="7"/>
+        <v>14.625</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="7"/>
+        <v>54.3</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="7"/>
+        <v>27.15</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="7"/>
+        <v>43.324999999999996</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -1946,12 +2226,52 @@
         <v>14.5</v>
       </c>
       <c r="E22">
-        <f t="shared" ref="E22:F22" si="7">MEDIAN(E5:E16)</f>
+        <f t="shared" ref="E22:Q22" si="8">MEDIAN(E5:E16)</f>
         <v>13.200000000000001</v>
       </c>
       <c r="F22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="8"/>
+        <v>14.7</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="8"/>
+        <v>14.9765625</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="8"/>
+        <v>16.375</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="8"/>
+        <v>82.262500000000003</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="8"/>
+        <v>41.131250000000001</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="8"/>
+        <v>8.9</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="8"/>
+        <v>44.5</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="8"/>
+        <v>65</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="8"/>
+        <v>19.5</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="8"/>
+        <v>67.28125</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2105,13 +2425,25 @@
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
   </mergeCells>
-  <conditionalFormatting sqref="P17:P20">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="P17:P19">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="34"/>
         <cfvo type="num" val="35"/>
         <color rgb="FFFF7128"/>
         <color rgb="FF92D050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P5:P16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -2134,43 +2466,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="52" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
+      <c r="A1" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
     </row>
     <row r="2" spans="1:23" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="52" t="str">
+      <c r="A2" s="64" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -2974,7 +3306,9 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
+      <c r="B19" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -2991,7 +3325,9 @@
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -3008,7 +3344,9 @@
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -3033,6 +3371,876 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3681973-B6A3-4484-A873-9D3A8F19A41F}">
+  <dimension ref="A1:S21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="7" max="7" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="4.5703125" customWidth="1"/>
+    <col min="11" max="11" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="24.75" x14ac:dyDescent="0.4">
+      <c r="A1" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+    </row>
+    <row r="2" spans="1:19" ht="24.75" x14ac:dyDescent="0.4">
+      <c r="A2" s="64" t="str">
+        <f>Marksheet!A2</f>
+        <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
+      </c>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="P4" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q4" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="R4" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="S4" s="45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="6">
+        <v>10</v>
+      </c>
+      <c r="D5" s="6">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6">
+        <v>15</v>
+      </c>
+      <c r="F5" s="6">
+        <v>15</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6">
+        <f>SUM(C5:J5)</f>
+        <v>50</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="O5" s="54">
+        <f t="shared" ref="O5:O17" si="0">SUMIF($C$3:$J$3, "CO1", $C5:$J5)</f>
+        <v>10</v>
+      </c>
+      <c r="P5" s="46">
+        <f t="shared" ref="P5:P17" si="1">SUMIF($C$3:$J$3, "CO2", $C5:$J5)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="46">
+        <f t="shared" ref="Q5:Q17" si="2">SUMIF($C$3:$J$3, "CO3", $C5:$J5)</f>
+        <v>25</v>
+      </c>
+      <c r="R5" s="46">
+        <f t="shared" ref="R5:R17" si="3">SUMIF($C$3:$J$3, "CO4", $C5:$J5)</f>
+        <v>15</v>
+      </c>
+      <c r="S5" s="46">
+        <f>SUM(O5:R5)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <f>'Mid Sem'!B6</f>
+        <v>590010833</v>
+      </c>
+      <c r="B6" s="5" t="str">
+        <f>'Mid Sem'!A6</f>
+        <v>Vansh Sharma</v>
+      </c>
+      <c r="C6" s="2">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="6">
+        <f t="shared" ref="K6:K18" si="4">SUM(C6:J6)</f>
+        <v>50</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="O6" s="55">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="P6" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="56">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="R6" s="56">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="S6" s="46">
+        <f t="shared" ref="S6:S17" si="5">SUM(O6:R6)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <f>'Mid Sem'!B7</f>
+        <v>590010853</v>
+      </c>
+      <c r="B7" s="5" t="str">
+        <f>'Mid Sem'!A7</f>
+        <v>Mokshika Saini</v>
+      </c>
+      <c r="C7" s="2">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2">
+        <v>5</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="6">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="O7" s="55">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="P7" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="56">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="R7" s="56">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="S7" s="46">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <f>'Mid Sem'!B8</f>
+        <v>590011314</v>
+      </c>
+      <c r="B8" s="5" t="str">
+        <f>'Mid Sem'!A8</f>
+        <v>Sakshi Sheshrao Charde</v>
+      </c>
+      <c r="C8" s="2">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2">
+        <v>15</v>
+      </c>
+      <c r="F8" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="6">
+        <f t="shared" si="4"/>
+        <v>49</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="O8" s="55">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="P8" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="56">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="R8" s="56">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="S8" s="46">
+        <f t="shared" si="5"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <f>'Mid Sem'!B9</f>
+        <v>590011462</v>
+      </c>
+      <c r="B9" s="5" t="str">
+        <f>'Mid Sem'!A9</f>
+        <v>Akash Vinodshirke</v>
+      </c>
+      <c r="C9" s="2">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2">
+        <v>15</v>
+      </c>
+      <c r="F9" s="2">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="6">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="O9" s="55">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="P9" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="56">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="R9" s="56">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="S9" s="46">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <f>'Mid Sem'!B10</f>
+        <v>590013559</v>
+      </c>
+      <c r="B10" s="5" t="str">
+        <f>'Mid Sem'!A10</f>
+        <v>Deevija Garg</v>
+      </c>
+      <c r="C10" s="2">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2">
+        <v>12</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="6">
+        <f t="shared" si="4"/>
+        <v>41</v>
+      </c>
+      <c r="L10" s="2"/>
+      <c r="O10" s="55">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="P10" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="56">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="R10" s="56">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="S10" s="46">
+        <f t="shared" si="5"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <f>'Mid Sem'!B11</f>
+        <v>590014314</v>
+      </c>
+      <c r="B11" s="5" t="str">
+        <f>'Mid Sem'!A11</f>
+        <v>Chandni Negi</v>
+      </c>
+      <c r="C11" s="2">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2">
+        <v>15</v>
+      </c>
+      <c r="F11" s="2">
+        <v>15</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="6">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="O11" s="55">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="P11" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="56">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="R11" s="56">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="S11" s="46">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <f>'Mid Sem'!B12</f>
+        <v>590016280</v>
+      </c>
+      <c r="B12" s="5" t="str">
+        <f>'Mid Sem'!A12</f>
+        <v>Divya Krishna</v>
+      </c>
+      <c r="C12" s="2">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2">
+        <v>10</v>
+      </c>
+      <c r="E12" s="2">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="6">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="O12" s="55">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="P12" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="56">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="R12" s="56">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="S12" s="46">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <f>'Mid Sem'!B13</f>
+        <v>590017181</v>
+      </c>
+      <c r="B13" s="5" t="str">
+        <f>'Mid Sem'!A13</f>
+        <v>Shubhangee Shukla</v>
+      </c>
+      <c r="C13" s="2">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2">
+        <v>10</v>
+      </c>
+      <c r="E13" s="2">
+        <v>12</v>
+      </c>
+      <c r="F13" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="6">
+        <f t="shared" si="4"/>
+        <v>47</v>
+      </c>
+      <c r="L13" s="2"/>
+      <c r="O13" s="55">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="P13" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="56">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="R13" s="56">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="S13" s="46">
+        <f t="shared" si="5"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <f>'Mid Sem'!B14</f>
+        <v>590017658</v>
+      </c>
+      <c r="B14" s="5" t="str">
+        <f>'Mid Sem'!A14</f>
+        <v>Heera Singh</v>
+      </c>
+      <c r="C14" s="2">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2">
+        <v>15</v>
+      </c>
+      <c r="F14" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="6">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="O14" s="55">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="P14" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="56">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="R14" s="56">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="S14" s="46">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <f>'Mid Sem'!B15</f>
+        <v>590017776</v>
+      </c>
+      <c r="B15" s="5" t="str">
+        <f>'Mid Sem'!A15</f>
+        <v>Abhineet Srivastava</v>
+      </c>
+      <c r="C15" s="2">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2">
+        <v>9</v>
+      </c>
+      <c r="E15" s="2">
+        <v>15</v>
+      </c>
+      <c r="F15" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="6">
+        <f t="shared" si="4"/>
+        <v>49</v>
+      </c>
+      <c r="L15" s="2"/>
+      <c r="O15" s="55">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="P15" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="56">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="R15" s="56">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="S15" s="46">
+        <f t="shared" si="5"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <f>'Mid Sem'!B16</f>
+        <v>590018198</v>
+      </c>
+      <c r="B16" s="5" t="str">
+        <f>'Mid Sem'!A16</f>
+        <v>Tanisha Chanani</v>
+      </c>
+      <c r="C16" s="2">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2">
+        <v>15</v>
+      </c>
+      <c r="F16" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="6">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="O16" s="55">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="P16" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="56">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="R16" s="56">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="S16" s="46">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <f>'Mid Sem'!B17</f>
+        <v>590018519</v>
+      </c>
+      <c r="B17" s="5" t="str">
+        <f>'Mid Sem'!A17</f>
+        <v>Rushil Soni</v>
+      </c>
+      <c r="C17" s="2">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2">
+        <v>12</v>
+      </c>
+      <c r="F17" s="2">
+        <v>15</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="6">
+        <f t="shared" si="4"/>
+        <v>47</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="O17" s="55">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="P17" s="56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="56">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="R17" s="56">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="S17" s="46">
+        <f t="shared" si="5"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="O18" s="55"/>
+      <c r="P18" s="55"/>
+      <c r="Q18" s="55"/>
+      <c r="R18" s="55"/>
+      <c r="S18" s="54"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="O19" s="55"/>
+      <c r="P19" s="55"/>
+      <c r="Q19" s="55"/>
+      <c r="R19" s="55"/>
+      <c r="S19" s="55"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="O20" s="55"/>
+      <c r="P20" s="55"/>
+      <c r="Q20" s="55"/>
+      <c r="R20" s="55"/>
+      <c r="S20" s="55"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="O21" s="55"/>
+      <c r="P21" s="55"/>
+      <c r="Q21" s="55"/>
+      <c r="R21" s="55"/>
+      <c r="S21" s="55"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC20399B-538A-4326-81D5-F56BB2966D2A}">
   <dimension ref="A1:W21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3046,45 +4254,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
     </row>
     <row r="2" spans="1:23" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="52" t="str">
+      <c r="A2" s="64" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -4018,7 +5226,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BA02827-4102-4501-99F8-C9B7DD668F03}">
   <dimension ref="A1:AM21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4034,81 +5242,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="52" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
-      <c r="V1" s="52"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="52"/>
-      <c r="Y1" s="52"/>
-      <c r="Z1" s="52"/>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="52"/>
-      <c r="AC1" s="52"/>
-      <c r="AD1" s="52"/>
-      <c r="AE1" s="52"/>
-      <c r="AF1" s="52"/>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
+      <c r="A1" s="64" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="64"/>
+      <c r="Z1" s="64"/>
+      <c r="AA1" s="64"/>
+      <c r="AB1" s="64"/>
+      <c r="AC1" s="64"/>
+      <c r="AD1" s="64"/>
+      <c r="AE1" s="64"/>
+      <c r="AF1" s="64"/>
+      <c r="AG1" s="64"/>
+      <c r="AH1" s="64"/>
     </row>
     <row r="2" spans="1:39" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="52" t="str">
+      <c r="A2" s="64" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="53"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="53"/>
-      <c r="AB2" s="53"/>
-      <c r="AC2" s="53"/>
-      <c r="AD2" s="53"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="53"/>
-      <c r="AG2" s="53"/>
-      <c r="AH2" s="53"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="65"/>
+      <c r="AB2" s="65"/>
+      <c r="AC2" s="65"/>
+      <c r="AD2" s="65"/>
+      <c r="AE2" s="65"/>
+      <c r="AF2" s="65"/>
+      <c r="AG2" s="65"/>
+      <c r="AH2" s="65"/>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -5933,7 +7141,1989 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B39D2C-73CD-4AE4-AA1F-0CD30E8A3469}">
+  <dimension ref="A1:AO21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="7" max="13" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="32" width="4.5703125" customWidth="1"/>
+    <col min="33" max="33" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="9.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:41" ht="24.75" x14ac:dyDescent="0.4">
+      <c r="A1" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="64"/>
+      <c r="Z1" s="64"/>
+      <c r="AA1" s="64"/>
+      <c r="AB1" s="64"/>
+      <c r="AC1" s="64"/>
+      <c r="AD1" s="64"/>
+      <c r="AE1" s="64"/>
+      <c r="AF1" s="64"/>
+      <c r="AG1" s="64"/>
+      <c r="AH1" s="64"/>
+    </row>
+    <row r="2" spans="1:41" ht="24.75" x14ac:dyDescent="0.4">
+      <c r="A2" s="64" t="str">
+        <f>Marksheet!A2</f>
+        <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
+      </c>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="65"/>
+      <c r="AB2" s="65"/>
+      <c r="AC2" s="65"/>
+      <c r="AD2" s="65"/>
+      <c r="AE2" s="65"/>
+      <c r="AF2" s="65"/>
+      <c r="AG2" s="65"/>
+      <c r="AH2" s="65"/>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG3" s="2"/>
+      <c r="AH3" s="2"/>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK4" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="AL4" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="AM4" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN4" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO4" s="45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="6">
+        <v>4</v>
+      </c>
+      <c r="D5" s="6">
+        <v>4</v>
+      </c>
+      <c r="E5" s="6">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6">
+        <v>4</v>
+      </c>
+      <c r="G5" s="6">
+        <v>4</v>
+      </c>
+      <c r="H5" s="6">
+        <v>4</v>
+      </c>
+      <c r="I5" s="6">
+        <v>4</v>
+      </c>
+      <c r="J5" s="6">
+        <v>4</v>
+      </c>
+      <c r="K5" s="6">
+        <v>4</v>
+      </c>
+      <c r="L5" s="6">
+        <v>4</v>
+      </c>
+      <c r="M5" s="6">
+        <v>10</v>
+      </c>
+      <c r="N5" s="6">
+        <v>10</v>
+      </c>
+      <c r="O5" s="6">
+        <v>10</v>
+      </c>
+      <c r="P5" s="6">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>10</v>
+      </c>
+      <c r="R5" s="6">
+        <v>10</v>
+      </c>
+      <c r="S5" s="6">
+        <v>10</v>
+      </c>
+      <c r="T5" s="6">
+        <v>10</v>
+      </c>
+      <c r="U5" s="6">
+        <v>10</v>
+      </c>
+      <c r="V5" s="6">
+        <v>10</v>
+      </c>
+      <c r="W5" s="6">
+        <v>10</v>
+      </c>
+      <c r="X5" s="6">
+        <v>10</v>
+      </c>
+      <c r="Y5" s="6">
+        <v>20</v>
+      </c>
+      <c r="Z5" s="6">
+        <v>20</v>
+      </c>
+      <c r="AA5" s="6">
+        <v>20</v>
+      </c>
+      <c r="AB5" s="6">
+        <v>20</v>
+      </c>
+      <c r="AC5" s="6">
+        <v>20</v>
+      </c>
+      <c r="AD5" s="6">
+        <v>20</v>
+      </c>
+      <c r="AE5" s="6">
+        <v>20</v>
+      </c>
+      <c r="AF5" s="6">
+        <v>20</v>
+      </c>
+      <c r="AG5" s="6">
+        <f>SUM(C5:AF5)</f>
+        <v>320</v>
+      </c>
+      <c r="AH5" s="6"/>
+      <c r="AK5" s="54">
+        <f>SUMIF($C$3:$AF$3, "CO1", $C5:$AF5)</f>
+        <v>28</v>
+      </c>
+      <c r="AL5" s="46">
+        <f>SUMIF($C$3:$AF$3, "CO2", $C5:$AF5)</f>
+        <v>170</v>
+      </c>
+      <c r="AM5" s="46">
+        <f>SUMIF($C$3:$AF$3, "CO3", $C5:$AF5)</f>
+        <v>54</v>
+      </c>
+      <c r="AN5" s="46">
+        <f>SUMIF($C$3:$AF$3, "CO4", $C5:$AF5)</f>
+        <v>68</v>
+      </c>
+      <c r="AO5" s="46">
+        <f>SUM(AK5:AN5)</f>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <f>'Mid Sem'!B6</f>
+        <v>590010833</v>
+      </c>
+      <c r="B6" s="5" t="str">
+        <f>'Mid Sem'!A6</f>
+        <v>Vansh Sharma</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2">
+        <v>4</v>
+      </c>
+      <c r="H6" s="2">
+        <v>4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>4</v>
+      </c>
+      <c r="J6" s="2">
+        <v>4</v>
+      </c>
+      <c r="K6" s="2">
+        <v>4</v>
+      </c>
+      <c r="L6" s="2">
+        <v>4</v>
+      </c>
+      <c r="M6" s="2">
+        <v>10</v>
+      </c>
+      <c r="N6" s="2">
+        <v>10</v>
+      </c>
+      <c r="O6" s="2">
+        <v>10</v>
+      </c>
+      <c r="P6" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>10</v>
+      </c>
+      <c r="R6" s="2">
+        <v>10</v>
+      </c>
+      <c r="S6" s="2">
+        <v>10</v>
+      </c>
+      <c r="T6" s="2">
+        <v>10</v>
+      </c>
+      <c r="U6" s="2">
+        <v>10</v>
+      </c>
+      <c r="V6" s="2">
+        <v>10</v>
+      </c>
+      <c r="W6" s="2">
+        <v>10</v>
+      </c>
+      <c r="X6" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD6" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE6" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF6" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG6" s="6">
+        <f t="shared" ref="AG6:AG18" si="0">SUM(C6:AF6)</f>
+        <v>320</v>
+      </c>
+      <c r="AH6" s="2"/>
+      <c r="AK6" s="55">
+        <f t="shared" ref="AK6:AK17" si="1">SUMIF($C$3:$AF$3, "CO1", $C6:$AF6)</f>
+        <v>28</v>
+      </c>
+      <c r="AL6" s="56">
+        <f t="shared" ref="AL6:AL17" si="2">SUMIF($C$3:$AF$3, "CO2", $C6:$AF6)</f>
+        <v>170</v>
+      </c>
+      <c r="AM6" s="56">
+        <f t="shared" ref="AM6:AM16" si="3">SUMIF($C$3:$AF$3, "CO3", $C6:$AF6)</f>
+        <v>54</v>
+      </c>
+      <c r="AN6" s="56">
+        <f t="shared" ref="AN6:AN17" si="4">SUMIF($C$3:$AF$3, "CO4", $C6:$AF6)</f>
+        <v>68</v>
+      </c>
+      <c r="AO6" s="46">
+        <f t="shared" ref="AO6:AO17" si="5">SUM(AK6:AN6)</f>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <f>'Mid Sem'!B7</f>
+        <v>590010853</v>
+      </c>
+      <c r="B7" s="5" t="str">
+        <f>'Mid Sem'!A7</f>
+        <v>Mokshika Saini</v>
+      </c>
+      <c r="C7" s="2">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2">
+        <v>4</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4</v>
+      </c>
+      <c r="I7" s="2">
+        <v>4</v>
+      </c>
+      <c r="J7" s="2">
+        <v>4</v>
+      </c>
+      <c r="K7" s="2">
+        <v>4</v>
+      </c>
+      <c r="L7" s="2">
+        <v>4</v>
+      </c>
+      <c r="M7" s="2">
+        <v>10</v>
+      </c>
+      <c r="N7" s="2">
+        <v>10</v>
+      </c>
+      <c r="O7" s="2">
+        <v>10</v>
+      </c>
+      <c r="P7" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>10</v>
+      </c>
+      <c r="R7" s="2">
+        <v>10</v>
+      </c>
+      <c r="S7" s="2">
+        <v>10</v>
+      </c>
+      <c r="T7" s="2">
+        <v>10</v>
+      </c>
+      <c r="U7" s="2">
+        <v>10</v>
+      </c>
+      <c r="V7" s="2">
+        <v>10</v>
+      </c>
+      <c r="W7" s="2">
+        <v>10</v>
+      </c>
+      <c r="X7" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE7" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF7" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG7" s="6">
+        <f t="shared" si="0"/>
+        <v>320</v>
+      </c>
+      <c r="AH7" s="2"/>
+      <c r="AK7" s="55">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="AL7" s="56">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+      <c r="AM7" s="56">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="AN7" s="56">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="AO7" s="46">
+        <f t="shared" si="5"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <f>'Mid Sem'!B8</f>
+        <v>590011314</v>
+      </c>
+      <c r="B8" s="5" t="str">
+        <f>'Mid Sem'!A8</f>
+        <v>Sakshi Sheshrao Charde</v>
+      </c>
+      <c r="C8" s="2">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2">
+        <v>4</v>
+      </c>
+      <c r="G8" s="2">
+        <v>4</v>
+      </c>
+      <c r="H8" s="2">
+        <v>4</v>
+      </c>
+      <c r="I8" s="2">
+        <v>4</v>
+      </c>
+      <c r="J8" s="2">
+        <v>4</v>
+      </c>
+      <c r="K8" s="2">
+        <v>4</v>
+      </c>
+      <c r="L8" s="2">
+        <v>4</v>
+      </c>
+      <c r="M8" s="2">
+        <v>10</v>
+      </c>
+      <c r="N8" s="2">
+        <v>10</v>
+      </c>
+      <c r="O8" s="2">
+        <v>10</v>
+      </c>
+      <c r="P8" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>10</v>
+      </c>
+      <c r="R8" s="2">
+        <v>9</v>
+      </c>
+      <c r="S8" s="2">
+        <v>10</v>
+      </c>
+      <c r="T8" s="2">
+        <v>10</v>
+      </c>
+      <c r="U8" s="2">
+        <v>10</v>
+      </c>
+      <c r="V8" s="2">
+        <v>10</v>
+      </c>
+      <c r="W8" s="2">
+        <v>10</v>
+      </c>
+      <c r="X8" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD8" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE8" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF8" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG8" s="6">
+        <v>319</v>
+      </c>
+      <c r="AH8" s="2"/>
+      <c r="AK8" s="55">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="AL8" s="56">
+        <f t="shared" si="2"/>
+        <v>169</v>
+      </c>
+      <c r="AM8" s="56">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="AN8" s="56">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="AO8" s="46">
+        <f t="shared" si="5"/>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <f>'Mid Sem'!B9</f>
+        <v>590011462</v>
+      </c>
+      <c r="B9" s="5" t="str">
+        <f>'Mid Sem'!A9</f>
+        <v>Akash Vinodshirke</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2">
+        <v>4</v>
+      </c>
+      <c r="G9" s="2">
+        <v>4</v>
+      </c>
+      <c r="H9" s="2">
+        <v>4</v>
+      </c>
+      <c r="I9" s="2">
+        <v>4</v>
+      </c>
+      <c r="J9" s="2">
+        <v>4</v>
+      </c>
+      <c r="K9" s="2">
+        <v>4</v>
+      </c>
+      <c r="L9" s="2">
+        <v>4</v>
+      </c>
+      <c r="M9" s="2">
+        <v>10</v>
+      </c>
+      <c r="N9" s="2">
+        <v>10</v>
+      </c>
+      <c r="O9" s="2">
+        <v>10</v>
+      </c>
+      <c r="P9" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>10</v>
+      </c>
+      <c r="R9" s="2">
+        <v>10</v>
+      </c>
+      <c r="S9" s="2">
+        <v>10</v>
+      </c>
+      <c r="T9" s="2">
+        <v>10</v>
+      </c>
+      <c r="U9" s="2">
+        <v>10</v>
+      </c>
+      <c r="V9" s="2">
+        <v>10</v>
+      </c>
+      <c r="W9" s="2">
+        <v>10</v>
+      </c>
+      <c r="X9" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE9" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF9" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG9" s="6">
+        <f t="shared" si="0"/>
+        <v>320</v>
+      </c>
+      <c r="AH9" s="2"/>
+      <c r="AK9" s="55">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="AL9" s="56">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+      <c r="AM9" s="56">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="AN9" s="56">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="AO9" s="46">
+        <f t="shared" si="5"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <f>'Mid Sem'!B10</f>
+        <v>590013559</v>
+      </c>
+      <c r="B10" s="5" t="str">
+        <f>'Mid Sem'!A10</f>
+        <v>Deevija Garg</v>
+      </c>
+      <c r="C10" s="2">
+        <v>4</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2">
+        <v>4</v>
+      </c>
+      <c r="H10" s="2">
+        <v>4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>4</v>
+      </c>
+      <c r="J10" s="2">
+        <v>4</v>
+      </c>
+      <c r="K10" s="2">
+        <v>4</v>
+      </c>
+      <c r="L10" s="2">
+        <v>4</v>
+      </c>
+      <c r="M10" s="2">
+        <v>10</v>
+      </c>
+      <c r="N10" s="2">
+        <v>10</v>
+      </c>
+      <c r="O10" s="2">
+        <v>10</v>
+      </c>
+      <c r="P10" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>10</v>
+      </c>
+      <c r="R10" s="2">
+        <v>10</v>
+      </c>
+      <c r="S10" s="2">
+        <v>10</v>
+      </c>
+      <c r="T10" s="2">
+        <v>10</v>
+      </c>
+      <c r="U10" s="2">
+        <v>10</v>
+      </c>
+      <c r="V10" s="2">
+        <v>10</v>
+      </c>
+      <c r="W10" s="2">
+        <v>10</v>
+      </c>
+      <c r="X10" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE10" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF10" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG10" s="6">
+        <f t="shared" si="0"/>
+        <v>320</v>
+      </c>
+      <c r="AH10" s="2"/>
+      <c r="AK10" s="55">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="AL10" s="56">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+      <c r="AM10" s="56">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="AN10" s="56">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="AO10" s="46">
+        <f t="shared" si="5"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <f>'Mid Sem'!B11</f>
+        <v>590014314</v>
+      </c>
+      <c r="B11" s="5" t="str">
+        <f>'Mid Sem'!A11</f>
+        <v>Chandni Negi</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+      <c r="AA11" s="2"/>
+      <c r="AB11" s="2"/>
+      <c r="AC11" s="2"/>
+      <c r="AD11" s="2"/>
+      <c r="AE11" s="2"/>
+      <c r="AF11" s="2"/>
+      <c r="AG11" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH11" s="2"/>
+      <c r="AK11" s="55">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL11" s="56">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM11" s="56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN11" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AO11" s="46">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <f>'Mid Sem'!B12</f>
+        <v>590016280</v>
+      </c>
+      <c r="B12" s="5" t="str">
+        <f>'Mid Sem'!A12</f>
+        <v>Divya Krishna</v>
+      </c>
+      <c r="C12" s="2">
+        <v>4</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2">
+        <v>4</v>
+      </c>
+      <c r="G12" s="2">
+        <v>4</v>
+      </c>
+      <c r="H12" s="2">
+        <v>4</v>
+      </c>
+      <c r="I12" s="2">
+        <v>4</v>
+      </c>
+      <c r="J12" s="2">
+        <v>4</v>
+      </c>
+      <c r="K12" s="2">
+        <v>4</v>
+      </c>
+      <c r="L12" s="2">
+        <v>4</v>
+      </c>
+      <c r="M12" s="2">
+        <v>10</v>
+      </c>
+      <c r="N12" s="2">
+        <v>10</v>
+      </c>
+      <c r="O12" s="2">
+        <v>10</v>
+      </c>
+      <c r="P12" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>10</v>
+      </c>
+      <c r="R12" s="2">
+        <v>10</v>
+      </c>
+      <c r="S12" s="2">
+        <v>10</v>
+      </c>
+      <c r="T12" s="2">
+        <v>10</v>
+      </c>
+      <c r="U12" s="2">
+        <v>10</v>
+      </c>
+      <c r="V12" s="2">
+        <v>10</v>
+      </c>
+      <c r="W12" s="2">
+        <v>10</v>
+      </c>
+      <c r="X12" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD12" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE12" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF12" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG12" s="6">
+        <f t="shared" si="0"/>
+        <v>320</v>
+      </c>
+      <c r="AH12" s="2"/>
+      <c r="AK12" s="55">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="AL12" s="56">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+      <c r="AM12" s="56">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="AN12" s="56">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="AO12" s="46">
+        <f t="shared" si="5"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <f>'Mid Sem'!B13</f>
+        <v>590017181</v>
+      </c>
+      <c r="B13" s="5" t="str">
+        <f>'Mid Sem'!A13</f>
+        <v>Shubhangee Shukla</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
+      <c r="Z13" s="2"/>
+      <c r="AA13" s="2"/>
+      <c r="AB13" s="2"/>
+      <c r="AC13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AE13" s="2"/>
+      <c r="AF13" s="2"/>
+      <c r="AG13" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH13" s="2"/>
+      <c r="AK13" s="55">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL13" s="56">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM13" s="56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN13" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AO13" s="46">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <f>'Mid Sem'!B14</f>
+        <v>590017658</v>
+      </c>
+      <c r="B14" s="5" t="str">
+        <f>'Mid Sem'!A14</f>
+        <v>Heera Singh</v>
+      </c>
+      <c r="C14" s="47">
+        <v>4</v>
+      </c>
+      <c r="D14" s="47">
+        <v>4</v>
+      </c>
+      <c r="E14" s="47">
+        <v>4</v>
+      </c>
+      <c r="F14" s="47">
+        <v>4</v>
+      </c>
+      <c r="G14" s="47">
+        <v>4</v>
+      </c>
+      <c r="H14" s="47">
+        <v>4</v>
+      </c>
+      <c r="I14" s="47">
+        <v>4</v>
+      </c>
+      <c r="J14" s="47">
+        <v>4</v>
+      </c>
+      <c r="K14" s="47">
+        <v>4</v>
+      </c>
+      <c r="L14" s="47">
+        <v>4</v>
+      </c>
+      <c r="M14" s="47">
+        <v>10</v>
+      </c>
+      <c r="N14" s="47">
+        <v>8</v>
+      </c>
+      <c r="O14" s="47">
+        <v>10</v>
+      </c>
+      <c r="P14" s="47">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="47">
+        <v>10</v>
+      </c>
+      <c r="R14" s="47">
+        <v>9</v>
+      </c>
+      <c r="S14" s="47">
+        <v>10</v>
+      </c>
+      <c r="T14" s="47">
+        <v>10</v>
+      </c>
+      <c r="U14" s="47">
+        <v>9</v>
+      </c>
+      <c r="V14" s="47">
+        <v>10</v>
+      </c>
+      <c r="W14" s="47">
+        <v>10</v>
+      </c>
+      <c r="X14" s="47">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="47">
+        <v>20</v>
+      </c>
+      <c r="Z14" s="47">
+        <v>18</v>
+      </c>
+      <c r="AA14" s="47">
+        <v>20</v>
+      </c>
+      <c r="AB14" s="47">
+        <v>20</v>
+      </c>
+      <c r="AC14" s="47">
+        <v>18</v>
+      </c>
+      <c r="AD14" s="47">
+        <v>20</v>
+      </c>
+      <c r="AE14" s="47">
+        <v>20</v>
+      </c>
+      <c r="AF14" s="47">
+        <v>20</v>
+      </c>
+      <c r="AG14" s="6">
+        <f t="shared" si="0"/>
+        <v>312</v>
+      </c>
+      <c r="AH14" s="2"/>
+      <c r="AK14" s="55">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="AL14" s="56">
+        <f t="shared" si="2"/>
+        <v>165</v>
+      </c>
+      <c r="AM14" s="56">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="AN14" s="56">
+        <f t="shared" si="4"/>
+        <v>65</v>
+      </c>
+      <c r="AO14" s="46">
+        <f t="shared" si="5"/>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <f>'Mid Sem'!B15</f>
+        <v>590017776</v>
+      </c>
+      <c r="B15" s="5" t="str">
+        <f>'Mid Sem'!A15</f>
+        <v>Abhineet Srivastava</v>
+      </c>
+      <c r="C15" s="47">
+        <v>4</v>
+      </c>
+      <c r="D15" s="47">
+        <v>4</v>
+      </c>
+      <c r="E15" s="47">
+        <v>4</v>
+      </c>
+      <c r="F15" s="47">
+        <v>4</v>
+      </c>
+      <c r="G15" s="47">
+        <v>4</v>
+      </c>
+      <c r="H15" s="47">
+        <v>4</v>
+      </c>
+      <c r="I15" s="47">
+        <v>4</v>
+      </c>
+      <c r="J15" s="47">
+        <v>4</v>
+      </c>
+      <c r="K15" s="47">
+        <v>4</v>
+      </c>
+      <c r="L15" s="47">
+        <v>4</v>
+      </c>
+      <c r="M15" s="47">
+        <v>8</v>
+      </c>
+      <c r="N15" s="47">
+        <v>6</v>
+      </c>
+      <c r="O15" s="47">
+        <v>10</v>
+      </c>
+      <c r="P15" s="47">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="47">
+        <v>10</v>
+      </c>
+      <c r="R15" s="47">
+        <v>10</v>
+      </c>
+      <c r="S15" s="47">
+        <v>10</v>
+      </c>
+      <c r="T15" s="47">
+        <v>10</v>
+      </c>
+      <c r="U15" s="47">
+        <v>10</v>
+      </c>
+      <c r="V15" s="47">
+        <v>10</v>
+      </c>
+      <c r="W15" s="47">
+        <v>10</v>
+      </c>
+      <c r="X15" s="47">
+        <v>10</v>
+      </c>
+      <c r="Y15" s="47">
+        <v>20</v>
+      </c>
+      <c r="Z15" s="47">
+        <v>20</v>
+      </c>
+      <c r="AA15" s="47">
+        <v>20</v>
+      </c>
+      <c r="AB15" s="47">
+        <v>20</v>
+      </c>
+      <c r="AC15" s="47">
+        <v>20</v>
+      </c>
+      <c r="AD15" s="47">
+        <v>20</v>
+      </c>
+      <c r="AE15" s="47">
+        <v>20</v>
+      </c>
+      <c r="AF15" s="47">
+        <v>20</v>
+      </c>
+      <c r="AG15" s="6">
+        <f t="shared" si="0"/>
+        <v>314</v>
+      </c>
+      <c r="AH15" s="2"/>
+      <c r="AK15" s="55">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="AL15" s="56">
+        <f t="shared" si="2"/>
+        <v>166</v>
+      </c>
+      <c r="AM15" s="56">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="AN15" s="56">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="AO15" s="46">
+        <f t="shared" si="5"/>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <f>'Mid Sem'!B16</f>
+        <v>590018198</v>
+      </c>
+      <c r="B16" s="5" t="str">
+        <f>'Mid Sem'!A16</f>
+        <v>Tanisha Chanani</v>
+      </c>
+      <c r="C16" s="2">
+        <v>4</v>
+      </c>
+      <c r="D16" s="2">
+        <v>4</v>
+      </c>
+      <c r="E16" s="2">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2">
+        <v>4</v>
+      </c>
+      <c r="G16" s="2">
+        <v>4</v>
+      </c>
+      <c r="H16" s="2">
+        <v>4</v>
+      </c>
+      <c r="I16" s="2">
+        <v>4</v>
+      </c>
+      <c r="J16" s="2">
+        <v>4</v>
+      </c>
+      <c r="K16" s="2">
+        <v>4</v>
+      </c>
+      <c r="L16" s="2">
+        <v>4</v>
+      </c>
+      <c r="M16" s="2">
+        <v>7</v>
+      </c>
+      <c r="N16" s="2">
+        <v>7</v>
+      </c>
+      <c r="O16" s="2">
+        <v>10</v>
+      </c>
+      <c r="P16" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>10</v>
+      </c>
+      <c r="R16" s="2">
+        <v>10</v>
+      </c>
+      <c r="S16" s="2">
+        <v>10</v>
+      </c>
+      <c r="T16" s="2">
+        <v>10</v>
+      </c>
+      <c r="U16" s="2">
+        <v>10</v>
+      </c>
+      <c r="V16" s="2">
+        <v>10</v>
+      </c>
+      <c r="W16" s="2">
+        <v>10</v>
+      </c>
+      <c r="X16" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD16" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE16" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF16" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG16" s="6">
+        <v>314</v>
+      </c>
+      <c r="AH16" s="2"/>
+      <c r="AK16" s="55">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="AL16" s="56">
+        <f t="shared" si="2"/>
+        <v>167</v>
+      </c>
+      <c r="AM16" s="56">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="AN16" s="56">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="AO16" s="46">
+        <f t="shared" si="5"/>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <f>'Mid Sem'!B17</f>
+        <v>590018519</v>
+      </c>
+      <c r="B17" s="5" t="str">
+        <f>'Mid Sem'!A17</f>
+        <v>Rushil Soni</v>
+      </c>
+      <c r="C17" s="2">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2">
+        <v>4</v>
+      </c>
+      <c r="E17" s="2">
+        <v>4</v>
+      </c>
+      <c r="F17" s="2">
+        <v>4</v>
+      </c>
+      <c r="G17" s="2">
+        <v>4</v>
+      </c>
+      <c r="H17" s="2">
+        <v>4</v>
+      </c>
+      <c r="I17" s="2">
+        <v>4</v>
+      </c>
+      <c r="J17" s="2">
+        <v>4</v>
+      </c>
+      <c r="K17" s="2">
+        <v>4</v>
+      </c>
+      <c r="L17" s="2">
+        <v>4</v>
+      </c>
+      <c r="M17" s="2">
+        <v>10</v>
+      </c>
+      <c r="N17" s="2">
+        <v>10</v>
+      </c>
+      <c r="O17" s="2">
+        <v>10</v>
+      </c>
+      <c r="P17" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>10</v>
+      </c>
+      <c r="R17" s="2">
+        <v>10</v>
+      </c>
+      <c r="S17" s="2">
+        <v>10</v>
+      </c>
+      <c r="T17" s="2">
+        <v>10</v>
+      </c>
+      <c r="U17" s="2">
+        <v>10</v>
+      </c>
+      <c r="V17" s="2">
+        <v>10</v>
+      </c>
+      <c r="W17" s="2">
+        <v>10</v>
+      </c>
+      <c r="X17" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD17" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE17" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF17" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG17" s="6">
+        <f t="shared" si="0"/>
+        <v>320</v>
+      </c>
+      <c r="AH17" s="2"/>
+      <c r="AK17" s="55">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="AL17" s="56">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+      <c r="AM17" s="56">
+        <f>SUMIF($C$3:$AF$3, "CO3", $C17:$AF17)</f>
+        <v>54</v>
+      </c>
+      <c r="AN17" s="56">
+        <f t="shared" si="4"/>
+        <v>68</v>
+      </c>
+      <c r="AO17" s="46">
+        <f t="shared" si="5"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+      <c r="AA18" s="2"/>
+      <c r="AB18" s="2"/>
+      <c r="AC18" s="2"/>
+      <c r="AD18" s="2"/>
+      <c r="AE18" s="2"/>
+      <c r="AF18" s="2"/>
+      <c r="AG18" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH18" s="2"/>
+      <c r="AK18" s="55"/>
+      <c r="AL18" s="55"/>
+      <c r="AM18" s="55"/>
+      <c r="AN18" s="55"/>
+      <c r="AO18" s="54"/>
+    </row>
+    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2"/>
+      <c r="AC19" s="2"/>
+      <c r="AD19" s="2"/>
+      <c r="AE19" s="2"/>
+      <c r="AF19" s="2"/>
+      <c r="AG19" s="2"/>
+      <c r="AH19" s="2"/>
+      <c r="AK19" s="55"/>
+      <c r="AL19" s="55"/>
+      <c r="AM19" s="55"/>
+      <c r="AN19" s="55"/>
+      <c r="AO19" s="55"/>
+    </row>
+    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+      <c r="AA20" s="2"/>
+      <c r="AB20" s="2"/>
+      <c r="AC20" s="2"/>
+      <c r="AD20" s="2"/>
+      <c r="AE20" s="2"/>
+      <c r="AF20" s="2"/>
+      <c r="AG20" s="2"/>
+      <c r="AH20" s="2"/>
+      <c r="AK20" s="55"/>
+      <c r="AL20" s="55"/>
+      <c r="AM20" s="55"/>
+      <c r="AN20" s="55"/>
+      <c r="AO20" s="55"/>
+    </row>
+    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+      <c r="AA21" s="2"/>
+      <c r="AB21" s="2"/>
+      <c r="AC21" s="2"/>
+      <c r="AD21" s="2"/>
+      <c r="AE21" s="2"/>
+      <c r="AF21" s="2"/>
+      <c r="AG21" s="2"/>
+      <c r="AH21" s="2"/>
+      <c r="AK21" s="55"/>
+      <c r="AL21" s="55"/>
+      <c r="AM21" s="55"/>
+      <c r="AN21" s="55"/>
+      <c r="AO21" s="55"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="A2:AH2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355320EC-5887-4CA4-8B00-C82693C60F77}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -5947,43 +9137,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
     </row>
     <row r="2" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="52" t="str">
+      <c r="A2" s="64" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -6151,34 +9341,34 @@
         <f>Marksheet!B5</f>
         <v>590010833</v>
       </c>
-      <c r="C6" s="57">
-        <v>4</v>
-      </c>
-      <c r="D6" s="57">
-        <v>3</v>
-      </c>
-      <c r="E6" s="57">
+      <c r="C6" s="52">
+        <v>4</v>
+      </c>
+      <c r="D6" s="52">
+        <v>3</v>
+      </c>
+      <c r="E6" s="52">
         <v>6</v>
       </c>
-      <c r="F6" s="57">
+      <c r="F6" s="52">
         <v>2</v>
       </c>
-      <c r="G6" s="57">
+      <c r="G6" s="52">
         <v>2</v>
       </c>
-      <c r="H6" s="57">
-        <v>4</v>
-      </c>
-      <c r="I6" s="57">
-        <v>4</v>
-      </c>
-      <c r="J6" s="57">
+      <c r="H6" s="52">
+        <v>4</v>
+      </c>
+      <c r="I6" s="52">
+        <v>4</v>
+      </c>
+      <c r="J6" s="52">
         <v>7</v>
       </c>
-      <c r="K6" s="57">
-        <v>10</v>
-      </c>
-      <c r="L6" s="57"/>
+      <c r="K6" s="52">
+        <v>10</v>
+      </c>
+      <c r="L6" s="52"/>
       <c r="M6" s="2"/>
       <c r="N6" s="9">
         <f>SUM(C6:K6)</f>
@@ -6215,16 +9405,16 @@
         <f>Marksheet!B6</f>
         <v>590010853</v>
       </c>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="57"/>
-      <c r="L7" s="57"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
       <c r="M7" s="2"/>
       <c r="N7" s="9">
         <f t="shared" ref="N7:N21" si="5">SUM(C7:H7)</f>
@@ -6261,34 +9451,34 @@
         <f>Marksheet!B7</f>
         <v>590011314</v>
       </c>
-      <c r="C8" s="57">
-        <v>4</v>
-      </c>
-      <c r="D8" s="57">
-        <v>4</v>
-      </c>
-      <c r="E8" s="57">
+      <c r="C8" s="52">
+        <v>4</v>
+      </c>
+      <c r="D8" s="52">
+        <v>4</v>
+      </c>
+      <c r="E8" s="52">
         <v>6</v>
       </c>
-      <c r="F8" s="57">
-        <v>4</v>
-      </c>
-      <c r="G8" s="57">
+      <c r="F8" s="52">
+        <v>4</v>
+      </c>
+      <c r="G8" s="52">
         <v>6</v>
       </c>
-      <c r="H8" s="57">
+      <c r="H8" s="52">
         <v>9</v>
       </c>
-      <c r="I8" s="57">
+      <c r="I8" s="52">
         <v>2</v>
       </c>
-      <c r="J8" s="57">
-        <v>5</v>
-      </c>
-      <c r="K8" s="57">
-        <v>0</v>
-      </c>
-      <c r="L8" s="57"/>
+      <c r="J8" s="52">
+        <v>5</v>
+      </c>
+      <c r="K8" s="52">
+        <v>0</v>
+      </c>
+      <c r="L8" s="52"/>
       <c r="M8" s="2"/>
       <c r="N8" s="9">
         <f>SUM(C8:K8)</f>
@@ -6325,34 +9515,34 @@
         <f>Marksheet!B8</f>
         <v>590011462</v>
       </c>
-      <c r="C9" s="57">
+      <c r="C9" s="52">
         <v>6</v>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="52">
         <v>6</v>
       </c>
-      <c r="E9" s="57">
+      <c r="E9" s="52">
         <v>6</v>
       </c>
-      <c r="F9" s="57">
+      <c r="F9" s="52">
         <v>6</v>
       </c>
-      <c r="G9" s="57">
+      <c r="G9" s="52">
         <v>6</v>
       </c>
-      <c r="H9" s="57">
+      <c r="H9" s="52">
         <v>15</v>
       </c>
-      <c r="I9" s="57">
+      <c r="I9" s="52">
         <v>12</v>
       </c>
-      <c r="J9" s="57">
+      <c r="J9" s="52">
         <v>15</v>
       </c>
-      <c r="K9" s="57">
+      <c r="K9" s="52">
         <v>20</v>
       </c>
-      <c r="L9" s="57"/>
+      <c r="L9" s="52"/>
       <c r="M9" s="2"/>
       <c r="N9" s="9">
         <f>SUM(C9:K9)</f>
@@ -6389,34 +9579,34 @@
         <f>Marksheet!B9</f>
         <v>590013559</v>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="52">
         <v>6</v>
       </c>
-      <c r="D10" s="57">
-        <v>5</v>
-      </c>
-      <c r="E10" s="57">
-        <v>5</v>
-      </c>
-      <c r="F10" s="57">
+      <c r="D10" s="52">
+        <v>5</v>
+      </c>
+      <c r="E10" s="52">
+        <v>5</v>
+      </c>
+      <c r="F10" s="52">
         <v>6</v>
       </c>
-      <c r="G10" s="57">
+      <c r="G10" s="52">
         <v>6</v>
       </c>
-      <c r="H10" s="57">
+      <c r="H10" s="52">
         <v>13</v>
       </c>
-      <c r="I10" s="57">
-        <v>3</v>
-      </c>
-      <c r="J10" s="57">
+      <c r="I10" s="52">
+        <v>3</v>
+      </c>
+      <c r="J10" s="52">
         <v>12</v>
       </c>
-      <c r="K10" s="57">
-        <v>5</v>
-      </c>
-      <c r="L10" s="57"/>
+      <c r="K10" s="52">
+        <v>5</v>
+      </c>
+      <c r="L10" s="52"/>
       <c r="M10" s="2"/>
       <c r="N10" s="9">
         <f>SUM(C10:K10)</f>
@@ -6453,34 +9643,34 @@
         <f>Marksheet!B10</f>
         <v>590014314</v>
       </c>
-      <c r="C11" s="58">
+      <c r="C11" s="53">
         <v>6</v>
       </c>
-      <c r="D11" s="58">
+      <c r="D11" s="53">
         <v>6</v>
       </c>
-      <c r="E11" s="58">
+      <c r="E11" s="53">
         <v>6</v>
       </c>
-      <c r="F11" s="58">
-        <v>4</v>
-      </c>
-      <c r="G11" s="58">
-        <v>4</v>
-      </c>
-      <c r="H11" s="58">
+      <c r="F11" s="53">
+        <v>4</v>
+      </c>
+      <c r="G11" s="53">
+        <v>4</v>
+      </c>
+      <c r="H11" s="53">
         <v>15</v>
       </c>
-      <c r="I11" s="57">
+      <c r="I11" s="52">
         <v>15</v>
       </c>
-      <c r="J11" s="57">
-        <v>10</v>
-      </c>
-      <c r="K11" s="57">
-        <v>10</v>
-      </c>
-      <c r="L11" s="57"/>
+      <c r="J11" s="52">
+        <v>10</v>
+      </c>
+      <c r="K11" s="52">
+        <v>10</v>
+      </c>
+      <c r="L11" s="52"/>
       <c r="M11" s="2"/>
       <c r="N11" s="9">
         <f>SUM(C11:K11)</f>
@@ -6517,28 +9707,28 @@
         <f>Marksheet!B11</f>
         <v>590016280</v>
       </c>
-      <c r="C12" s="57">
+      <c r="C12" s="52">
         <v>6</v>
       </c>
-      <c r="D12" s="57">
+      <c r="D12" s="52">
         <v>6</v>
       </c>
-      <c r="E12" s="57">
-        <v>4</v>
-      </c>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57">
+      <c r="E12" s="52">
+        <v>4</v>
+      </c>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52">
         <v>6</v>
       </c>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57">
+      <c r="H12" s="52"/>
+      <c r="I12" s="52">
         <v>7</v>
       </c>
-      <c r="J12" s="57">
+      <c r="J12" s="52">
         <v>6</v>
       </c>
-      <c r="K12" s="57"/>
-      <c r="L12" s="57"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="52"/>
       <c r="M12" s="2"/>
       <c r="N12" s="9">
         <f>SUM(C12:J12)</f>
@@ -6575,34 +9765,34 @@
         <f>Marksheet!B12</f>
         <v>590017181</v>
       </c>
-      <c r="C13" s="57">
+      <c r="C13" s="52">
         <v>6</v>
       </c>
-      <c r="D13" s="57">
-        <v>3</v>
-      </c>
-      <c r="E13" s="57">
-        <v>5</v>
-      </c>
-      <c r="F13" s="57">
-        <v>3</v>
-      </c>
-      <c r="G13" s="57">
-        <v>4</v>
-      </c>
-      <c r="H13" s="57">
-        <v>5</v>
-      </c>
-      <c r="I13" s="57">
-        <v>0</v>
-      </c>
-      <c r="J13" s="57">
-        <v>4</v>
-      </c>
-      <c r="K13" s="57">
-        <v>0</v>
-      </c>
-      <c r="L13" s="57"/>
+      <c r="D13" s="52">
+        <v>3</v>
+      </c>
+      <c r="E13" s="52">
+        <v>5</v>
+      </c>
+      <c r="F13" s="52">
+        <v>3</v>
+      </c>
+      <c r="G13" s="52">
+        <v>4</v>
+      </c>
+      <c r="H13" s="52">
+        <v>5</v>
+      </c>
+      <c r="I13" s="52">
+        <v>0</v>
+      </c>
+      <c r="J13" s="52">
+        <v>4</v>
+      </c>
+      <c r="K13" s="52">
+        <v>0</v>
+      </c>
+      <c r="L13" s="52"/>
       <c r="M13" s="2"/>
       <c r="N13" s="9">
         <f>SUM(C13:K13)</f>
@@ -6639,34 +9829,34 @@
         <f>Marksheet!B13</f>
         <v>590017658</v>
       </c>
-      <c r="C14" s="57">
+      <c r="C14" s="52">
         <v>6</v>
       </c>
-      <c r="D14" s="57">
-        <v>5</v>
-      </c>
-      <c r="E14" s="57">
+      <c r="D14" s="52">
+        <v>5</v>
+      </c>
+      <c r="E14" s="52">
         <v>6</v>
       </c>
-      <c r="F14" s="57">
-        <v>4</v>
-      </c>
-      <c r="G14" s="57">
-        <v>4</v>
-      </c>
-      <c r="H14" s="57">
-        <v>10</v>
-      </c>
-      <c r="I14" s="57">
-        <v>5</v>
-      </c>
-      <c r="J14" s="57">
+      <c r="F14" s="52">
+        <v>4</v>
+      </c>
+      <c r="G14" s="52">
+        <v>4</v>
+      </c>
+      <c r="H14" s="52">
+        <v>10</v>
+      </c>
+      <c r="I14" s="52">
+        <v>5</v>
+      </c>
+      <c r="J14" s="52">
         <v>7</v>
       </c>
-      <c r="K14" s="57">
-        <v>0</v>
-      </c>
-      <c r="L14" s="57"/>
+      <c r="K14" s="52">
+        <v>0</v>
+      </c>
+      <c r="L14" s="52"/>
       <c r="M14" s="2"/>
       <c r="N14" s="9">
         <f>SUM(C14:K14)</f>
@@ -6703,34 +9893,34 @@
         <f>Marksheet!B14</f>
         <v>590017776</v>
       </c>
-      <c r="C15" s="57">
+      <c r="C15" s="52">
         <v>6</v>
       </c>
-      <c r="D15" s="57">
+      <c r="D15" s="52">
         <v>6</v>
       </c>
-      <c r="E15" s="57">
+      <c r="E15" s="52">
         <v>6</v>
       </c>
-      <c r="F15" s="57">
-        <v>5</v>
-      </c>
-      <c r="G15" s="57">
+      <c r="F15" s="52">
+        <v>5</v>
+      </c>
+      <c r="G15" s="52">
         <v>6</v>
       </c>
-      <c r="H15" s="57">
+      <c r="H15" s="52">
         <v>13</v>
       </c>
-      <c r="I15" s="57">
+      <c r="I15" s="52">
         <v>15</v>
       </c>
-      <c r="J15" s="57">
+      <c r="J15" s="52">
         <v>15</v>
       </c>
-      <c r="K15" s="57">
+      <c r="K15" s="52">
         <v>20</v>
       </c>
-      <c r="L15" s="57"/>
+      <c r="L15" s="52"/>
       <c r="M15" s="2"/>
       <c r="N15" s="9">
         <f>SUM(C15:K15)</f>
@@ -6767,34 +9957,34 @@
         <f>Marksheet!B15</f>
         <v>590018198</v>
       </c>
-      <c r="C16" s="57">
+      <c r="C16" s="52">
         <v>6</v>
       </c>
-      <c r="D16" s="57">
-        <v>5</v>
-      </c>
-      <c r="E16" s="57">
+      <c r="D16" s="52">
+        <v>5</v>
+      </c>
+      <c r="E16" s="52">
         <v>6</v>
       </c>
-      <c r="F16" s="57">
+      <c r="F16" s="52">
         <v>6</v>
       </c>
-      <c r="G16" s="57">
-        <v>4</v>
-      </c>
-      <c r="H16" s="57">
+      <c r="G16" s="52">
+        <v>4</v>
+      </c>
+      <c r="H16" s="52">
         <v>14</v>
       </c>
-      <c r="I16" s="57">
+      <c r="I16" s="52">
         <v>15</v>
       </c>
-      <c r="J16" s="57">
+      <c r="J16" s="52">
         <v>15</v>
       </c>
-      <c r="K16" s="57">
+      <c r="K16" s="52">
         <v>15</v>
       </c>
-      <c r="L16" s="57"/>
+      <c r="L16" s="52"/>
       <c r="M16" s="2"/>
       <c r="N16" s="9">
         <f>SUM(C16:K16)</f>
@@ -6831,34 +10021,34 @@
         <f>Marksheet!B16</f>
         <v>590018519</v>
       </c>
-      <c r="C17" s="57">
-        <v>5</v>
-      </c>
-      <c r="D17" s="57">
-        <v>4</v>
-      </c>
-      <c r="E17" s="57">
-        <v>3</v>
-      </c>
-      <c r="F17" s="57">
+      <c r="C17" s="52">
+        <v>5</v>
+      </c>
+      <c r="D17" s="52">
+        <v>4</v>
+      </c>
+      <c r="E17" s="52">
+        <v>3</v>
+      </c>
+      <c r="F17" s="52">
         <v>1</v>
       </c>
-      <c r="G17" s="57">
-        <v>4</v>
-      </c>
-      <c r="H17" s="57">
+      <c r="G17" s="52">
+        <v>4</v>
+      </c>
+      <c r="H17" s="52">
         <v>2</v>
       </c>
-      <c r="I17" s="57">
-        <v>4</v>
-      </c>
-      <c r="J17" s="57">
-        <v>4</v>
-      </c>
-      <c r="K17" s="57">
-        <v>5</v>
-      </c>
-      <c r="L17" s="57"/>
+      <c r="I17" s="52">
+        <v>4</v>
+      </c>
+      <c r="J17" s="52">
+        <v>4</v>
+      </c>
+      <c r="K17" s="52">
+        <v>5</v>
+      </c>
+      <c r="L17" s="52"/>
       <c r="M17" s="2"/>
       <c r="N17" s="9">
         <f>SUM(C17:K17)</f>
@@ -6889,16 +10079,16 @@
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="14"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="57"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="52"/>
       <c r="M18" s="2"/>
       <c r="N18" s="9">
         <f t="shared" si="5"/>
@@ -6929,16 +10119,16 @@
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="14"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="52"/>
+      <c r="L19" s="52"/>
       <c r="M19" s="2"/>
       <c r="N19" s="9">
         <f t="shared" si="5"/>
@@ -7104,9 +10294,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AFC0182-6626-4C28-AE12-3805CD8061D9}">
-  <dimension ref="A1:O21"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3EC6E4-73FE-451F-9DA1-2F8671C4541C}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -7116,65 +10309,65 @@
     <col min="15" max="15" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="52" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-    </row>
-    <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="52" t="str">
+    <row r="1" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
+      <c r="A1" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+    </row>
+    <row r="2" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
+      <c r="A2" s="64" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>48</v>
@@ -7186,15 +10379,13 @@
         <v>49</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M3" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="M3" s="3"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>50</v>
       </c>
@@ -7231,1087 +10422,91 @@
       <c r="L4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>62</v>
-      </c>
+      <c r="M4" s="4"/>
       <c r="N4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="O4" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R4" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="S4" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="T4" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="U4" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="V4" s="45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" s="6">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H5" s="6">
-        <v>15</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="I5" s="6">
+        <v>5</v>
+      </c>
+      <c r="J5" s="6">
+        <v>5</v>
+      </c>
+      <c r="K5" s="6">
+        <v>5</v>
+      </c>
+      <c r="L5" s="6">
+        <v>5</v>
+      </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6">
-        <v>10</v>
+        <f>SUM(C5:L5)</f>
+        <v>40</v>
       </c>
       <c r="O5" s="6"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <f>'Mid Sem'!B6</f>
-        <v>590010833</v>
-      </c>
-      <c r="B6" s="5" t="str">
-        <f>'Mid Sem'!A6</f>
-        <v>Vansh Sharma</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <f>'Mid Sem'!B7</f>
-        <v>590010853</v>
-      </c>
-      <c r="B7" s="5" t="str">
-        <f>'Mid Sem'!A7</f>
-        <v>Mokshika Saini</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <f>'Mid Sem'!B8</f>
-        <v>590011314</v>
-      </c>
-      <c r="B8" s="5" t="str">
-        <f>'Mid Sem'!A8</f>
-        <v>Sakshi Sheshrao Charde</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
-        <f>'Mid Sem'!B9</f>
-        <v>590011462</v>
-      </c>
-      <c r="B9" s="5" t="str">
-        <f>'Mid Sem'!A9</f>
-        <v>Akash Vinodshirke</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
-        <f>'Mid Sem'!B10</f>
-        <v>590013559</v>
-      </c>
-      <c r="B10" s="5" t="str">
-        <f>'Mid Sem'!A10</f>
-        <v>Deevija Garg</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
-        <f>'Mid Sem'!B11</f>
-        <v>590014314</v>
-      </c>
-      <c r="B11" s="5" t="str">
-        <f>'Mid Sem'!A11</f>
-        <v>Chandni Negi</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <f>'Mid Sem'!B12</f>
-        <v>590016280</v>
-      </c>
-      <c r="B12" s="5" t="str">
-        <f>'Mid Sem'!A12</f>
-        <v>Divya Krishna</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
-        <f>'Mid Sem'!B13</f>
-        <v>590017181</v>
-      </c>
-      <c r="B13" s="5" t="str">
-        <f>'Mid Sem'!A13</f>
-        <v>Shubhangee Shukla</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
-        <f>'Mid Sem'!B14</f>
-        <v>590017658</v>
-      </c>
-      <c r="B14" s="5" t="str">
-        <f>'Mid Sem'!A14</f>
-        <v>Heera Singh</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
-        <f>'Mid Sem'!B15</f>
-        <v>590017776</v>
-      </c>
-      <c r="B15" s="5" t="str">
-        <f>'Mid Sem'!A15</f>
-        <v>Abhineet Srivastava</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
-        <f>'Mid Sem'!B16</f>
-        <v>590018198</v>
-      </c>
-      <c r="B16" s="5" t="str">
-        <f>'Mid Sem'!A16</f>
-        <v>Tanisha Chanani</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <f>'Mid Sem'!B17</f>
-        <v>590018519</v>
-      </c>
-      <c r="B17" s="5" t="str">
-        <f>'Mid Sem'!A17</f>
-        <v>Rushil Soni</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D596BA-28B6-4E3D-B4DD-BA2BE95F4450}">
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="13" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="52" t="s">
+      <c r="R5" s="54">
+        <v>0</v>
+      </c>
+      <c r="S5" s="46">
+        <f>SUM(C5,H5)</f>
         <v>8</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-    </row>
-    <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="52" t="str">
-        <f>Marksheet!A2</f>
-        <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
-      </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="6">
-        <v>5</v>
-      </c>
-      <c r="D5" s="6">
-        <v>5</v>
-      </c>
-      <c r="E5" s="6">
-        <v>5</v>
-      </c>
-      <c r="F5" s="6">
-        <v>5</v>
-      </c>
-      <c r="G5" s="6">
-        <v>15</v>
-      </c>
-      <c r="H5" s="6">
-        <v>15</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6">
-        <v>10</v>
-      </c>
-      <c r="O5" s="6"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <f>'Mid Sem'!B6</f>
-        <v>590010833</v>
-      </c>
-      <c r="B6" s="5" t="str">
-        <f>'Mid Sem'!A6</f>
-        <v>Vansh Sharma</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <f>'Mid Sem'!B7</f>
-        <v>590010853</v>
-      </c>
-      <c r="B7" s="5" t="str">
-        <f>'Mid Sem'!A7</f>
-        <v>Mokshika Saini</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <f>'Mid Sem'!B8</f>
-        <v>590011314</v>
-      </c>
-      <c r="B8" s="5" t="str">
-        <f>'Mid Sem'!A8</f>
-        <v>Sakshi Sheshrao Charde</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
-        <f>'Mid Sem'!B9</f>
-        <v>590011462</v>
-      </c>
-      <c r="B9" s="5" t="str">
-        <f>'Mid Sem'!A9</f>
-        <v>Akash Vinodshirke</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
-        <f>'Mid Sem'!B10</f>
-        <v>590013559</v>
-      </c>
-      <c r="B10" s="5" t="str">
-        <f>'Mid Sem'!A10</f>
-        <v>Deevija Garg</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
-        <f>'Mid Sem'!B11</f>
-        <v>590014314</v>
-      </c>
-      <c r="B11" s="5" t="str">
-        <f>'Mid Sem'!A11</f>
-        <v>Chandni Negi</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <f>'Mid Sem'!B12</f>
-        <v>590016280</v>
-      </c>
-      <c r="B12" s="5" t="str">
-        <f>'Mid Sem'!A12</f>
-        <v>Divya Krishna</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
-        <f>'Mid Sem'!B13</f>
-        <v>590017181</v>
-      </c>
-      <c r="B13" s="5" t="str">
-        <f>'Mid Sem'!A13</f>
-        <v>Shubhangee Shukla</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
-        <f>'Mid Sem'!B14</f>
-        <v>590017658</v>
-      </c>
-      <c r="B14" s="5" t="str">
-        <f>'Mid Sem'!A14</f>
-        <v>Heera Singh</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
-        <f>'Mid Sem'!B15</f>
-        <v>590017776</v>
-      </c>
-      <c r="B15" s="5" t="str">
-        <f>'Mid Sem'!A15</f>
-        <v>Abhineet Srivastava</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
-        <f>'Mid Sem'!B16</f>
-        <v>590018198</v>
-      </c>
-      <c r="B16" s="5" t="str">
-        <f>'Mid Sem'!A16</f>
-        <v>Tanisha Chanani</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <f>'Mid Sem'!B17</f>
-        <v>590018519</v>
-      </c>
-      <c r="B17" s="5" t="str">
-        <f>'Mid Sem'!A17</f>
-        <v>Rushil Soni</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3EC6E4-73FE-451F-9DA1-2F8671C4541C}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="13" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-    </row>
-    <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="52" t="str">
-        <f>Marksheet!A2</f>
-        <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
-      </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6">
-        <v>30</v>
-      </c>
-      <c r="O5" s="6"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="T5" s="46">
+        <f>SUM(D5,E5,I5,J5)</f>
+        <v>16</v>
+      </c>
+      <c r="U5" s="46">
+        <f>SUM(K5,L5,G5,F5)</f>
+        <v>16</v>
+      </c>
+      <c r="V5" s="46">
+        <f>SUM(R5:U5)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>Marksheet!B5</f>
         <v>590010833</v>
@@ -8320,21 +10515,63 @@
         <f>Marksheet!A5</f>
         <v>Vansh Sharma</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2">
+        <v>5</v>
+      </c>
+      <c r="J6" s="2">
+        <v>2</v>
+      </c>
+      <c r="K6" s="2">
+        <v>4</v>
+      </c>
+      <c r="L6" s="2">
+        <v>4</v>
+      </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="6"/>
+      <c r="N6" s="6">
+        <f t="shared" ref="N6:N17" si="0">SUM(C6:L6)</f>
+        <v>33</v>
+      </c>
       <c r="O6" s="2"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R6" s="58">
+        <v>0</v>
+      </c>
+      <c r="S6" s="59">
+        <f t="shared" ref="S6:S17" si="1">SUM(C6,H6)</f>
+        <v>6</v>
+      </c>
+      <c r="T6" s="59">
+        <f t="shared" ref="T6:T17" si="2">SUM(D6,E6,I6,J6)</f>
+        <v>13</v>
+      </c>
+      <c r="U6" s="59">
+        <f t="shared" ref="U6:U17" si="3">SUM(K6,L6,G6,F6)</f>
+        <v>14</v>
+      </c>
+      <c r="V6" s="46">
+        <f t="shared" ref="V6:V17" si="4">SUM(R6:U6)</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>Marksheet!B6</f>
         <v>590010853</v>
@@ -8343,21 +10580,63 @@
         <f>Marksheet!A6</f>
         <v>Mokshika Saini</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>3</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="I7" s="2">
+        <v>4</v>
+      </c>
+      <c r="J7" s="2">
+        <v>3</v>
+      </c>
+      <c r="K7" s="2">
+        <v>3</v>
+      </c>
+      <c r="L7" s="2">
+        <v>3</v>
+      </c>
       <c r="M7" s="2"/>
-      <c r="N7" s="6"/>
+      <c r="N7" s="6">
+        <f t="shared" si="0"/>
+        <v>32.5</v>
+      </c>
       <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R7" s="58">
+        <v>0</v>
+      </c>
+      <c r="S7" s="59">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+      <c r="T7" s="59">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="U7" s="59">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="V7" s="46">
+        <f t="shared" si="4"/>
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>Marksheet!B7</f>
         <v>590011314</v>
@@ -8366,21 +10645,63 @@
         <f>Marksheet!A7</f>
         <v>Sakshi Sheshrao Charde</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>3</v>
+      </c>
+      <c r="G8" s="2">
+        <v>3</v>
+      </c>
+      <c r="H8" s="2">
+        <v>5</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5</v>
+      </c>
+      <c r="J8" s="2">
+        <v>4</v>
+      </c>
+      <c r="K8" s="2">
+        <v>2</v>
+      </c>
+      <c r="L8" s="2">
+        <v>4</v>
+      </c>
       <c r="M8" s="2"/>
-      <c r="N8" s="6"/>
+      <c r="N8" s="6">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
       <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R8" s="58">
+        <v>0</v>
+      </c>
+      <c r="S8" s="59">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T8" s="59">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="U8" s="59">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="V8" s="46">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>Marksheet!B8</f>
         <v>590011462</v>
@@ -8389,21 +10710,63 @@
         <f>Marksheet!A8</f>
         <v>Akash Vinodshirke</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2">
+        <v>3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3</v>
+      </c>
+      <c r="H9" s="2">
+        <v>5</v>
+      </c>
+      <c r="I9" s="2">
+        <v>5</v>
+      </c>
+      <c r="J9" s="2">
+        <v>5</v>
+      </c>
+      <c r="K9" s="2">
+        <v>5</v>
+      </c>
+      <c r="L9" s="2">
+        <v>5</v>
+      </c>
       <c r="M9" s="2"/>
-      <c r="N9" s="6"/>
+      <c r="N9" s="6">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
       <c r="O9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R9" s="58">
+        <v>0</v>
+      </c>
+      <c r="S9" s="59">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T9" s="59">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="U9" s="59">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="V9" s="46">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>Marksheet!B9</f>
         <v>590013559</v>
@@ -8412,21 +10775,63 @@
         <f>Marksheet!A9</f>
         <v>Deevija Garg</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>3</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2">
+        <v>5</v>
+      </c>
+      <c r="K10" s="2">
+        <v>4</v>
+      </c>
+      <c r="L10" s="2">
+        <v>4</v>
+      </c>
       <c r="M10" s="2"/>
-      <c r="N10" s="6"/>
+      <c r="N10" s="6">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
       <c r="O10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R10" s="58">
+        <v>0</v>
+      </c>
+      <c r="S10" s="59">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="T10" s="59">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="U10" s="59">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="V10" s="46">
+        <f t="shared" si="4"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>Marksheet!B10</f>
         <v>590014314</v>
@@ -8435,21 +10840,63 @@
         <f>Marksheet!A10</f>
         <v>Chandni Negi</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2">
+        <v>3</v>
+      </c>
+      <c r="H11" s="2">
+        <v>5</v>
+      </c>
+      <c r="I11" s="2">
+        <v>2</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <v>3</v>
+      </c>
+      <c r="L11" s="2">
+        <v>4</v>
+      </c>
       <c r="M11" s="2"/>
-      <c r="N11" s="6"/>
+      <c r="N11" s="6">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
       <c r="O11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R11" s="58">
+        <v>0</v>
+      </c>
+      <c r="S11" s="59">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T11" s="59">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="U11" s="59">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="V11" s="46">
+        <f t="shared" si="4"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f>Marksheet!B11</f>
         <v>590016280</v>
@@ -8458,21 +10905,63 @@
         <f>Marksheet!A11</f>
         <v>Divya Krishna</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2">
+        <v>3</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>5</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <v>5</v>
+      </c>
+      <c r="K12" s="2">
+        <v>5</v>
+      </c>
+      <c r="L12" s="2">
+        <v>5</v>
+      </c>
       <c r="M12" s="2"/>
-      <c r="N12" s="6"/>
+      <c r="N12" s="6">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
       <c r="O12" s="2"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R12" s="58">
+        <v>0</v>
+      </c>
+      <c r="S12" s="59">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T12" s="59">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="U12" s="59">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="V12" s="46">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f>Marksheet!B12</f>
         <v>590017181</v>
@@ -8481,21 +10970,63 @@
         <f>Marksheet!A12</f>
         <v>Shubhangee Shukla</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
+        <v>3</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2">
+        <v>3</v>
+      </c>
+      <c r="H13" s="2">
+        <v>4</v>
+      </c>
+      <c r="I13" s="2">
+        <v>4</v>
+      </c>
+      <c r="J13" s="2">
+        <v>3</v>
+      </c>
+      <c r="K13" s="2">
+        <v>2</v>
+      </c>
+      <c r="L13" s="2">
+        <v>2</v>
+      </c>
       <c r="M13" s="2"/>
-      <c r="N13" s="6"/>
+      <c r="N13" s="6">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
       <c r="O13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R13" s="58">
+        <v>0</v>
+      </c>
+      <c r="S13" s="59">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="T13" s="59">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="U13" s="59">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="V13" s="46">
+        <f t="shared" si="4"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f>Marksheet!B13</f>
         <v>590017658</v>
@@ -8504,21 +11035,63 @@
         <f>Marksheet!A13</f>
         <v>Heera Singh</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2">
+        <v>3</v>
+      </c>
+      <c r="H14" s="2">
+        <v>3</v>
+      </c>
+      <c r="I14" s="2">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2">
+        <v>5</v>
+      </c>
+      <c r="K14" s="2">
+        <v>4</v>
+      </c>
+      <c r="L14" s="2">
+        <v>2</v>
+      </c>
       <c r="M14" s="2"/>
-      <c r="N14" s="6"/>
+      <c r="N14" s="6">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
       <c r="O14" s="2"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R14" s="58">
+        <v>0</v>
+      </c>
+      <c r="S14" s="59">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="T14" s="59">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="U14" s="59">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="V14" s="46">
+        <f t="shared" si="4"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <f>Marksheet!B14</f>
         <v>590017776</v>
@@ -8527,21 +11100,63 @@
         <f>Marksheet!A14</f>
         <v>Abhineet Srivastava</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2">
+        <v>3</v>
+      </c>
+      <c r="H15" s="2">
+        <v>5</v>
+      </c>
+      <c r="I15" s="2">
+        <v>5</v>
+      </c>
+      <c r="J15" s="2">
+        <v>5</v>
+      </c>
+      <c r="K15" s="2">
+        <v>5</v>
+      </c>
+      <c r="L15" s="2">
+        <v>5</v>
+      </c>
       <c r="M15" s="2"/>
-      <c r="N15" s="6"/>
+      <c r="N15" s="6">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
       <c r="O15" s="2"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R15" s="58">
+        <v>0</v>
+      </c>
+      <c r="S15" s="59">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T15" s="59">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="U15" s="59">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="V15" s="46">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <f>Marksheet!B15</f>
         <v>590018198</v>
@@ -8550,21 +11165,63 @@
         <f>Marksheet!A15</f>
         <v>Tanisha Chanani</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
+      <c r="C16" s="2">
+        <v>3</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2">
+        <v>3</v>
+      </c>
+      <c r="H16" s="2">
+        <v>5</v>
+      </c>
+      <c r="I16" s="2">
+        <v>5</v>
+      </c>
+      <c r="J16" s="2">
+        <v>5</v>
+      </c>
+      <c r="K16" s="2">
+        <v>5</v>
+      </c>
+      <c r="L16" s="2">
+        <v>3</v>
+      </c>
       <c r="M16" s="2"/>
-      <c r="N16" s="6"/>
+      <c r="N16" s="6">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
       <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R16" s="58">
+        <v>0</v>
+      </c>
+      <c r="S16" s="59">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T16" s="59">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="U16" s="59">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="V16" s="46">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f>Marksheet!B16</f>
         <v>590018519</v>
@@ -8573,21 +11230,63 @@
         <f>Marksheet!A16</f>
         <v>Rushil Soni</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
+      <c r="C17" s="2">
+        <v>3</v>
+      </c>
+      <c r="D17" s="2">
+        <v>3</v>
+      </c>
+      <c r="E17" s="2">
+        <v>3</v>
+      </c>
+      <c r="F17" s="2">
+        <v>3</v>
+      </c>
+      <c r="G17" s="2">
+        <v>3</v>
+      </c>
+      <c r="H17" s="2">
+        <v>4</v>
+      </c>
+      <c r="I17" s="2">
+        <v>3</v>
+      </c>
+      <c r="J17" s="2">
+        <v>3</v>
+      </c>
+      <c r="K17" s="2">
+        <v>4</v>
+      </c>
+      <c r="L17" s="2">
+        <v>4</v>
+      </c>
       <c r="M17" s="2"/>
-      <c r="N17" s="6"/>
+      <c r="N17" s="6">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
       <c r="O17" s="2"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R17" s="58">
+        <v>0</v>
+      </c>
+      <c r="S17" s="59">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="T17" s="59">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="U17" s="59">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="V17" s="46">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="2"/>
@@ -8603,8 +11302,13 @@
       <c r="M18" s="2"/>
       <c r="N18" s="6"/>
       <c r="O18" s="2"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R18" s="55"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="55"/>
+      <c r="U18" s="55"/>
+      <c r="V18" s="59"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="2"/>
@@ -8620,8 +11324,13 @@
       <c r="M19" s="2"/>
       <c r="N19" s="6"/>
       <c r="O19" s="2"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R19" s="55"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="55"/>
+      <c r="U19" s="55"/>
+      <c r="V19" s="55"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="2"/>
@@ -8637,8 +11346,13 @@
       <c r="M20" s="2"/>
       <c r="N20" s="6"/>
       <c r="O20" s="2"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R20" s="55"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="55"/>
+      <c r="U20" s="55"/>
+      <c r="V20" s="55"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="2"/>
@@ -8654,6 +11368,11 @@
       <c r="M21" s="2"/>
       <c r="N21" s="6"/>
       <c r="O21" s="2"/>
+      <c r="R21" s="55"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="55"/>
+      <c r="U21" s="55"/>
+      <c r="V21" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8679,43 +11398,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="52" t="str">
+      <c r="A2" s="64" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="18"/>
@@ -8856,18 +11575,43 @@
         <f>'Mid Sem'!A6</f>
         <v>Vansh Sharma</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="6"/>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2">
+        <v>4</v>
+      </c>
+      <c r="J6" s="2">
+        <v>6</v>
+      </c>
+      <c r="K6" s="2">
+        <v>10</v>
+      </c>
+      <c r="L6" s="2">
+        <v>4</v>
+      </c>
+      <c r="M6" s="2">
+        <v>10</v>
+      </c>
+      <c r="N6" s="6">
+        <f t="shared" ref="N6:N18" si="0">SUM(C6:M6)</f>
+        <v>51</v>
+      </c>
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -8879,18 +11623,43 @@
         <f>'Mid Sem'!A7</f>
         <v>Mokshika Saini</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="6"/>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2">
+        <v>4</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>3</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2">
+        <v>8</v>
+      </c>
+      <c r="N7" s="6">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -8902,18 +11671,43 @@
         <f>'Mid Sem'!A8</f>
         <v>Sakshi Sheshrao Charde</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="6"/>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>2</v>
+      </c>
+      <c r="J8" s="2">
+        <v>2</v>
+      </c>
+      <c r="K8" s="2">
+        <v>4</v>
+      </c>
+      <c r="L8" s="2">
+        <v>6</v>
+      </c>
+      <c r="M8" s="2">
+        <v>7</v>
+      </c>
+      <c r="N8" s="6">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -8925,18 +11719,43 @@
         <f>'Mid Sem'!A9</f>
         <v>Akash Vinodshirke</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="6"/>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2">
+        <v>4</v>
+      </c>
+      <c r="G9" s="2">
+        <v>4</v>
+      </c>
+      <c r="H9" s="2">
+        <v>10</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8</v>
+      </c>
+      <c r="J9" s="2">
+        <v>10</v>
+      </c>
+      <c r="K9" s="2">
+        <v>10</v>
+      </c>
+      <c r="L9" s="2">
+        <v>18</v>
+      </c>
+      <c r="M9" s="2">
+        <v>19</v>
+      </c>
+      <c r="N9" s="6">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -8948,18 +11767,43 @@
         <f>'Mid Sem'!A10</f>
         <v>Deevija Garg</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="6"/>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2">
+        <v>4</v>
+      </c>
+      <c r="H10" s="2">
+        <v>6</v>
+      </c>
+      <c r="I10" s="2">
+        <v>10</v>
+      </c>
+      <c r="J10" s="2">
+        <v>8</v>
+      </c>
+      <c r="K10" s="2">
+        <v>7</v>
+      </c>
+      <c r="L10" s="2">
+        <v>14</v>
+      </c>
+      <c r="M10" s="2">
+        <v>6</v>
+      </c>
+      <c r="N10" s="6">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -8971,18 +11815,43 @@
         <f>'Mid Sem'!A11</f>
         <v>Chandni Negi</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="6"/>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2">
+        <v>4</v>
+      </c>
+      <c r="H11" s="2">
+        <v>6</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7</v>
+      </c>
+      <c r="J11" s="2">
+        <v>3</v>
+      </c>
+      <c r="K11" s="2">
+        <v>10</v>
+      </c>
+      <c r="L11" s="2">
+        <v>11</v>
+      </c>
+      <c r="M11" s="2">
+        <v>13</v>
+      </c>
+      <c r="N11" s="6">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -8994,18 +11863,43 @@
         <f>'Mid Sem'!A12</f>
         <v>Divya Krishna</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="6"/>
+      <c r="C12" s="2">
+        <v>4</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2">
+        <v>4</v>
+      </c>
+      <c r="G12" s="2">
+        <v>4</v>
+      </c>
+      <c r="H12" s="2">
+        <v>7</v>
+      </c>
+      <c r="I12" s="2">
+        <v>10</v>
+      </c>
+      <c r="J12" s="2">
+        <v>10</v>
+      </c>
+      <c r="K12" s="2">
+        <v>6</v>
+      </c>
+      <c r="L12" s="2">
+        <v>13</v>
+      </c>
+      <c r="M12" s="2">
+        <v>5</v>
+      </c>
+      <c r="N12" s="6">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -9017,18 +11911,43 @@
         <f>'Mid Sem'!A13</f>
         <v>Shubhangee Shukla</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="6"/>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2">
+        <v>4</v>
+      </c>
+      <c r="G13" s="2">
+        <v>3</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <v>7</v>
+      </c>
+      <c r="L13" s="2">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2">
+        <v>10</v>
+      </c>
+      <c r="N13" s="6">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
       <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -9040,18 +11959,41 @@
         <f>'Mid Sem'!A14</f>
         <v>Heera Singh</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2">
+        <v>4</v>
+      </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="6"/>
+      <c r="E14" s="2">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2">
+        <v>4</v>
+      </c>
+      <c r="H14" s="2">
+        <v>3</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
+        <v>7</v>
+      </c>
+      <c r="L14" s="2">
+        <v>15</v>
+      </c>
+      <c r="M14" s="2">
+        <v>17</v>
+      </c>
+      <c r="N14" s="6">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
       <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -9063,18 +12005,43 @@
         <f>'Mid Sem'!A15</f>
         <v>Abhineet Srivastava</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="6"/>
+      <c r="C15" s="2">
+        <v>4</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4</v>
+      </c>
+      <c r="G15" s="2">
+        <v>4</v>
+      </c>
+      <c r="H15" s="2">
+        <v>4</v>
+      </c>
+      <c r="I15" s="2">
+        <v>4</v>
+      </c>
+      <c r="J15" s="2">
+        <v>6</v>
+      </c>
+      <c r="K15" s="2">
+        <v>10</v>
+      </c>
+      <c r="L15" s="2">
+        <v>12</v>
+      </c>
+      <c r="M15" s="2">
+        <v>12</v>
+      </c>
+      <c r="N15" s="6">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
       <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -9086,18 +12053,43 @@
         <f>'Mid Sem'!A16</f>
         <v>Tanisha Chanani</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="6"/>
+      <c r="C16" s="2">
+        <v>4</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2">
+        <v>4</v>
+      </c>
+      <c r="G16" s="2">
+        <v>3</v>
+      </c>
+      <c r="H16" s="2">
+        <v>7</v>
+      </c>
+      <c r="I16" s="2">
+        <v>10</v>
+      </c>
+      <c r="J16" s="2">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2">
+        <v>10</v>
+      </c>
+      <c r="L16" s="2">
+        <v>18</v>
+      </c>
+      <c r="M16" s="2">
+        <v>18</v>
+      </c>
+      <c r="N16" s="6">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -9109,18 +12101,43 @@
         <f>'Mid Sem'!A17</f>
         <v>Rushil Soni</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="6"/>
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2">
+        <v>3</v>
+      </c>
+      <c r="H17" s="2">
+        <v>5</v>
+      </c>
+      <c r="I17" s="2">
+        <v>5</v>
+      </c>
+      <c r="J17" s="2">
+        <v>4</v>
+      </c>
+      <c r="K17" s="2">
+        <v>10</v>
+      </c>
+      <c r="L17" s="2">
+        <v>4</v>
+      </c>
+      <c r="M17" s="2">
+        <v>4</v>
+      </c>
+      <c r="N17" s="6">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -9137,7 +12154,10 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
-      <c r="N18" s="6"/>
+      <c r="N18" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="O18" s="2"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
